--- a/context_DB/MOZ_context_db.xlsx
+++ b/context_DB/MOZ_context_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL70"/>
+  <dimension ref="A1:BL88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1493,68 +1493,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MZ0107</t>
+          <t>MZ0106</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>MZ0110</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MZ0107;MZ0110;MZ0403;MZ0711</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>51.68</v>
-      </c>
-      <c r="I7" t="n">
-        <v>47.09</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="L7" t="n">
-        <v>38.35</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.39</v>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
@@ -1582,20 +1544,60 @@
       <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Cabo Delgado</t>
+        </is>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>MZ01</t>
+        </is>
+      </c>
       <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>Islamic State Mozambique (ISM)</t>
+        </is>
+      </c>
       <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Civilians (Mozambique)</t>
+        </is>
+      </c>
       <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>On 8 February 2025, ISM militants injured one resident during an attack that displaced residents from neighboring villages to the Chai administrative post (Macomia, Cabo Delgado), where they were subsequently housed at the arts and crafts school. Extent of injuries unknown/not reported.</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>Macomia</t>
+        </is>
+      </c>
       <c r="BL7" t="n">
         <v>0</v>
       </c>
@@ -1603,7 +1605,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MZ0108</t>
+          <t>MZ0107</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -1612,58 +1614,58 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MZ1122</t>
+          <t>MZ0110</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
+          <t>MZ0107;MZ0110;MZ0403;MZ0711</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>62.3</v>
+        <v>51.68</v>
       </c>
       <c r="I8" t="n">
-        <v>36.07</v>
+        <v>47.09</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="K8" t="n">
-        <v>1.64</v>
+        <v>0.18</v>
       </c>
       <c r="L8" t="n">
-        <v>88.95</v>
+        <v>38.35</v>
       </c>
       <c r="M8" t="n">
-        <v>1.38</v>
+        <v>0.35</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="U8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6.47</v>
+        <v>0.39</v>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
@@ -1692,60 +1694,20 @@
       <c r="AU8" t="inlineStr"/>
       <c r="AV8" t="inlineStr"/>
       <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Cabo Delgado</t>
-        </is>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>MZ01</t>
-        </is>
-      </c>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>Battles</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>Armed clash</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>Islamic State Mozambique (ISM)</t>
-        </is>
-      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>Police Forces of Mozambique (1990-)</t>
-        </is>
-      </c>
+      <c r="BG8" t="inlineStr"/>
       <c r="BH8" t="inlineStr"/>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>On 7 December 2024, at least 12 ISM, armed with medium machine guns and at least one rocket-propelled grenade launcher, attacked the headquarters of the administrative post in Muaguide (Meluco, Cabo Delgado). They damaged several public infrastructures: they destroyed the house of the head of the post chief, they burned the secondary school, the police station, several homes and 2 motorbikes. They also looted various products from shops and medicines from the health center. 1 police officer was injured. Inhabitants left the village and walked 50 kilometers until Meluco. IS claimed to have burned three 'Christian' houses and a shop for 'Christians'.</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>2024-12-07</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>Meluco</t>
-        </is>
-      </c>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
       <c r="BL8" t="n">
         <v>0</v>
       </c>
@@ -1753,7 +1715,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MZ0109</t>
+          <t>MZ0108</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -1762,7 +1724,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MZ0112</t>
+          <t>MZ1122</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1771,49 +1733,49 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>52.81</v>
+        <v>62.3</v>
       </c>
       <c r="I9" t="n">
-        <v>45.45</v>
+        <v>36.07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="L9" t="n">
-        <v>22.05</v>
+        <v>88.95</v>
       </c>
       <c r="M9" t="n">
-        <v>2.56</v>
+        <v>1.38</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="T9" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V9" t="n">
-        <v>0.46</v>
+        <v>6.47</v>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
@@ -1848,7 +1810,7 @@
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
         <v>1</v>
@@ -1861,12 +1823,12 @@
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>Violence against civilians</t>
+          <t>Battles</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Armed clash</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -1877,27 +1839,23 @@
       <c r="BF9" t="inlineStr"/>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Civilians (Mozambique)</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>Farmers (Mozambique); Students (Mozambique)</t>
-        </is>
-      </c>
+          <t>Police Forces of Mozambique (1990-)</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>On 6 March 2024, Islamist militia killed six civilians, including at least one farmer, in Pulo (Metuge, Cabo Delgado). They locked several children (exact number unknown) in a classroom at a primary school. They abducted nine students who were leaving Metuge secondary school and set several houses on fire. Residents of Pulo, Nacuta, Ponto A, Chauli, Walopwana, and Muisse fled towards Pemba and Metuge. The Islamic State claimed the attack and burning of a 'Christian' school and 29 houses. Captives were released by the militia some hours after the attack.</t>
+          <t>On 7 December 2024, at least 12 ISM, armed with medium machine guns and at least one rocket-propelled grenade launcher, attacked the headquarters of the administrative post in Muaguide (Meluco, Cabo Delgado). They damaged several public infrastructures: they destroyed the house of the head of the post chief, they burned the secondary school, the police station, several homes and 2 motorbikes. They also looted various products from shops and medicines from the health center. 1 police officer was injured. Inhabitants left the village and walked 50 kilometers until Meluco. IS claimed to have burned three 'Christian' houses and a shop for 'Christians'.</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-12-07</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>Metuge</t>
+          <t>Meluco</t>
         </is>
       </c>
       <c r="BL9" t="n">
@@ -1907,7 +1865,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MZ0110</t>
+          <t>MZ0109</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -1916,43 +1874,43 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MZ0403</t>
+          <t>MZ0112</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MZ0107;MZ0110;MZ0403;MZ0711</t>
+          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>74.86</v>
+        <v>52.81</v>
       </c>
       <c r="I10" t="n">
-        <v>18.29</v>
+        <v>45.45</v>
       </c>
       <c r="J10" t="n">
-        <v>6.86</v>
+        <v>1.73</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>27.64</v>
+        <v>22.05</v>
       </c>
       <c r="M10" t="n">
-        <v>3.43</v>
+        <v>2.56</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.57</v>
+        <v>0.15</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.5</v>
+        <v>1.02</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1961,100 +1919,38 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.57</v>
+        <v>0.15</v>
       </c>
       <c r="U10" t="n">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>2025-04-07</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>April 2025: An educator was killed in an attack on a village by unidentified armed men.</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>Unspecified Location</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>NSA</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>Unidentified Armed Actor</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>Firearms</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
+        <v>0.46</v>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
       <c r="AU10" t="inlineStr"/>
       <c r="AV10" t="inlineStr"/>
       <c r="AW10" t="inlineStr"/>
@@ -2064,10 +1960,10 @@
         </is>
       </c>
       <c r="AY10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>1</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>2</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -2077,17 +1973,17 @@
       <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>Strategic developments ---- Violence against civilians</t>
+          <t>Violence against civilians</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>Other ---- Attack</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>Islamic State Mozambique (ISM) ---- Islamic State Mozambique (ISM)</t>
+          <t>Islamic State Mozambique (ISM)</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr"/>
@@ -2098,22 +1994,22 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>Teachers (Mozambique)</t>
+          <t>Farmers (Mozambique); Students (Mozambique)</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Non-violent activity: Around 26 February 2025 (week of), ISM militants made threats to teachers and demanded that children attend madrassas rather than secular schools in several villages in Mocimboa da Praia (coded as Ulo, Mocimboa da Praia, Mocimboa da Praia, Cabo Delgado). In Ulo village near the district headquarters, militants told teachers they wanted madrassa activities; teachers reported them to the district management and the militants left the area. In Malimbi, the militants held a meeting with the residents and demanded the madrassas, took down a community flag, and told the population to flee. In Unduva village, the militants stole phones and held a meeting with about 30 residents. Many of the school teachers and directors from the areas fled to Pemba for safety. ---- On 7 April 2025, 4 ISM militants stabbed and killed 1 teacher, abducted 3 people, and stole goods from homes in Ntotwe (Mocimboa da Praia, Cabo Delgado). The militants encountered the teacher while he was drinking alcohol, asked him where the village leader's house was, and when he claimed not to know 1 militant killed him. Some residents fled into the surrounding bush. ISM claimed the attack was on 1 Christian.</t>
+          <t>On 6 March 2024, Islamist militia killed six civilians, including at least one farmer, in Pulo (Metuge, Cabo Delgado). They locked several children (exact number unknown) in a classroom at a primary school. They abducted nine students who were leaving Metuge secondary school and set several houses on fire. Residents of Pulo, Nacuta, Ponto A, Chauli, Walopwana, and Muisse fled towards Pemba and Metuge. The Islamic State claimed the attack and burning of a 'Christian' school and 29 houses. Captives were released by the militia some hours after the attack.</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>2025-02-26 ---- 2025-04-07</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>Mocimboa da Praia</t>
+          <t>Metuge</t>
         </is>
       </c>
       <c r="BL10" t="n">
@@ -2123,7 +2019,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MZ0111</t>
+          <t>MZ0110</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -2132,43 +2028,43 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MZ0809</t>
+          <t>MZ0403</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
+          <t>MZ0107;MZ0110;MZ0403;MZ0711</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>57.51</v>
+        <v>74.86</v>
       </c>
       <c r="I11" t="n">
-        <v>38.68</v>
+        <v>18.29</v>
       </c>
       <c r="J11" t="n">
-        <v>3.09</v>
+        <v>6.86</v>
       </c>
       <c r="K11" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>34.61</v>
+        <v>27.64</v>
       </c>
       <c r="M11" t="n">
-        <v>0.58</v>
+        <v>3.43</v>
       </c>
       <c r="N11" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.27</v>
+        <v>0.57</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.64</v>
+        <v>2.5</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2177,55 +2073,161 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>4.12</v>
+        <v>0.57</v>
       </c>
       <c r="U11" t="n">
-        <v>0.21</v>
+        <v>0.83</v>
       </c>
       <c r="V11" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>April 2025: An educator was killed in an attack on a village by unidentified armed men.</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>Unspecified Location</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>Unidentified Armed Actor</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Firearms</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="AU11" t="inlineStr"/>
       <c r="AV11" t="inlineStr"/>
       <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr"/>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Cabo Delgado</t>
+        </is>
+      </c>
+      <c r="AY11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>MZ01</t>
+        </is>
+      </c>
       <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>Strategic developments ---- Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>Other ---- Attack</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>Islamic State Mozambique (ISM) ---- Islamic State Mozambique (ISM)</t>
+        </is>
+      </c>
       <c r="BF11" t="inlineStr"/>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
-      <c r="BI11" t="inlineStr"/>
-      <c r="BJ11" t="inlineStr"/>
-      <c r="BK11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Civilians (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>Teachers (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>Non-violent activity: Around 26 February 2025 (week of), ISM militants made threats to teachers and demanded that children attend madrassas rather than secular schools in several villages in Mocimboa da Praia (coded as Ulo, Mocimboa da Praia, Mocimboa da Praia, Cabo Delgado). In Ulo village near the district headquarters, militants told teachers they wanted madrassa activities; teachers reported them to the district management and the militants left the area. In Malimbi, the militants held a meeting with the residents and demanded the madrassas, took down a community flag, and told the population to flee. In Unduva village, the militants stole phones and held a meeting with about 30 residents. Many of the school teachers and directors from the areas fled to Pemba for safety. ---- On 7 April 2025, 4 ISM militants stabbed and killed 1 teacher, abducted 3 people, and stole goods from homes in Ntotwe (Mocimboa da Praia, Cabo Delgado). The militants encountered the teacher while he was drinking alcohol, asked him where the village leader's house was, and when he claimed not to know 1 militant killed him. Some residents fled into the surrounding bush. ISM claimed the attack was on 1 Christian.</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>2025-02-26 ---- 2025-04-07</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>Mocimboa da Praia</t>
+        </is>
+      </c>
       <c r="BL11" t="n">
         <v>0</v>
       </c>
@@ -2233,7 +2235,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MZ0112</t>
+          <t>MZ0111</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -2242,58 +2244,58 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MZ0109</t>
+          <t>MZ0809</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
+          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>78.64</v>
+        <v>57.51</v>
       </c>
       <c r="I12" t="n">
-        <v>18.48</v>
+        <v>38.68</v>
       </c>
       <c r="J12" t="n">
-        <v>2.66</v>
+        <v>3.09</v>
       </c>
       <c r="K12" t="n">
-        <v>0.23</v>
+        <v>0.72</v>
       </c>
       <c r="L12" t="n">
-        <v>32.58</v>
+        <v>34.61</v>
       </c>
       <c r="M12" t="n">
-        <v>2.47</v>
+        <v>0.58</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="O12" t="n">
-        <v>0.08</v>
+        <v>0.27</v>
       </c>
       <c r="P12" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.43</v>
+        <v>0.64</v>
       </c>
       <c r="R12" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.12</v>
+        <v>4.12</v>
       </c>
       <c r="U12" t="n">
-        <v>0.12</v>
+        <v>0.21</v>
       </c>
       <c r="V12" t="n">
-        <v>0.23</v>
+        <v>0.72</v>
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
@@ -2343,7 +2345,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MZ0113</t>
+          <t>MZ0112</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -2352,7 +2354,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MZ0116</t>
+          <t>MZ0109</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2361,197 +2363,91 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>59.43</v>
+        <v>78.64</v>
       </c>
       <c r="I13" t="n">
-        <v>26.49</v>
+        <v>18.48</v>
       </c>
       <c r="J13" t="n">
-        <v>1.67</v>
+        <v>2.66</v>
       </c>
       <c r="K13" t="n">
-        <v>12.41</v>
+        <v>0.23</v>
       </c>
       <c r="L13" t="n">
-        <v>73.23999999999999</v>
+        <v>32.58</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>2.47</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="P13" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.31</v>
+        <v>0.43</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="S13" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.79</v>
+        <v>0.12</v>
       </c>
       <c r="U13" t="n">
-        <v>0.32</v>
+        <v>0.12</v>
       </c>
       <c r="V13" t="n">
-        <v>25.81</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>October 2024: Educators and students felt threatened and fled their classrooms when Islamist militia fired shots to test weapons.</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Education Building </t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>NSA</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>Islamic State</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>Firearms</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>School: No Further Details</t>
-        </is>
-      </c>
+        <v>0.23</v>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
       <c r="AU13" t="inlineStr"/>
       <c r="AV13" t="inlineStr"/>
       <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Cabo Delgado</t>
-        </is>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>MZ01</t>
-        </is>
-      </c>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>Strategic developments</t>
-        </is>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>Islamic State Mozambique (ISM)</t>
-        </is>
-      </c>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
       <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>Civilians (Mozambique)</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>Students (Mozambique); Teachers (Mozambique)</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
-        <is>
-          <t>Other: On 2 October 2024, Islamist militia (likely due to their recent presence in the area) fired shots to test weapons in the district of Muidumbe (location coded to Muidumbe, Muidumbe, Cabo Delgado). Teachers and students fled to classrooms. No violent interactions reported.</t>
-        </is>
-      </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="BK13" t="inlineStr">
-        <is>
-          <t>Muidumbe</t>
-        </is>
-      </c>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
       <c r="BL13" t="n">
         <v>0</v>
       </c>
@@ -2559,7 +2455,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MZ0114</t>
+          <t>MZ0113</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -2568,100 +2464,206 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MZ0704</t>
+          <t>MZ0116</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
+          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>80.59999999999999</v>
+        <v>59.43</v>
       </c>
       <c r="I14" t="n">
-        <v>18.39</v>
+        <v>26.49</v>
       </c>
       <c r="J14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="K14" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="L14" t="n">
+        <v>73.23999999999999</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="V14" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>44.71</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>October 2024: Educators and students felt threatened and fled their classrooms when Islamist militia fired shots to test weapons.</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building </t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>Islamic State</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Firearms</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>School: No Further Details</t>
+        </is>
+      </c>
       <c r="AU14" t="inlineStr"/>
       <c r="AV14" t="inlineStr"/>
       <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="inlineStr"/>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cabo Delgado</t>
+        </is>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>MZ01</t>
+        </is>
+      </c>
       <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>Strategic developments</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>Islamic State Mozambique (ISM)</t>
+        </is>
+      </c>
       <c r="BF14" t="inlineStr"/>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
-      <c r="BI14" t="inlineStr"/>
-      <c r="BJ14" t="inlineStr"/>
-      <c r="BK14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Civilians (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>Students (Mozambique); Teachers (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>Other: On 2 October 2024, Islamist militia (likely due to their recent presence in the area) fired shots to test weapons in the district of Muidumbe (location coded to Muidumbe, Muidumbe, Cabo Delgado). Teachers and students fled to classrooms. No violent interactions reported.</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>Muidumbe</t>
+        </is>
+      </c>
       <c r="BL14" t="n">
         <v>0</v>
       </c>
@@ -2669,7 +2671,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MZ0115</t>
+          <t>MZ0114</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -2678,43 +2680,43 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MZ0815</t>
+          <t>MZ0704</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
+          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>40.64</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>54.19</v>
+        <v>18.39</v>
       </c>
       <c r="J15" t="n">
-        <v>4.19</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>45.56999999999999</v>
+        <v>44.71</v>
       </c>
       <c r="M15" t="n">
-        <v>2.04</v>
+        <v>0.25</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2723,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.33</v>
+        <v>0.12</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
@@ -2779,7 +2781,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MZ0207</t>
+          <t>MZ0115</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -2788,7 +2790,7 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MZ0101</t>
+          <t>MZ0815</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2797,28 +2799,28 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>76.36</v>
+        <v>40.64</v>
       </c>
       <c r="I16" t="n">
-        <v>18.18</v>
+        <v>54.19</v>
       </c>
       <c r="J16" t="n">
-        <v>5.45</v>
+        <v>4.19</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="L16" t="n">
-        <v>24.72</v>
+        <v>45.56999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>14.54</v>
+        <v>2.04</v>
       </c>
       <c r="N16" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -2827,19 +2829,19 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="U16" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.56</v>
+        <v>2.27</v>
       </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
@@ -2868,64 +2870,20 @@
       <c r="AU16" t="inlineStr"/>
       <c r="AV16" t="inlineStr"/>
       <c r="AW16" t="inlineStr"/>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Gaza</t>
-        </is>
-      </c>
-      <c r="AY16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>MZ02</t>
-        </is>
-      </c>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
       <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>Protests ---- Protests</t>
-        </is>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>Peaceful protest ---- Excessive force against protesters</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>Protesters (Mozambique) ---- Protesters (Mozambique)</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>Teachers (Mozambique) ---- Labor Group (Mozambique)</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>Police Forces of Mozambique (1990-)</t>
-        </is>
-      </c>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
       <c r="BH16" t="inlineStr"/>
-      <c r="BI16" t="inlineStr">
-        <is>
-          <t>Around 1 February 2024 (as reported), teachers marched in Xai-Xai (Xai-Xai, Gaza) for better working conditions, including the payment of extra hours by the government, and against overcrowded classrooms. ---- On 26 March 2025, over 250 public bus drivers and conductors stopped work and protested in Xai-Xai (Xai-Xai, Gaza) against the installation of a traffic checkpoint in the city. Police shot and killed 1 man while trying to disperse the protesters who were demanding for the deactivation of a traffic checkpoint/inspection post in Potinha neighborhood, claiming that police use it to illegally extort money from drivers. During the demonstrations, traffic on all routes stopped and many schools closed.</t>
-        </is>
-      </c>
-      <c r="BJ16" t="inlineStr">
-        <is>
-          <t>2024-02-01 ---- 2025-03-26</t>
-        </is>
-      </c>
-      <c r="BK16" t="inlineStr">
-        <is>
-          <t>Xai-Xai</t>
-        </is>
-      </c>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
       <c r="BL16" t="n">
         <v>0</v>
       </c>
@@ -2933,147 +2891,175 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MZ0301</t>
+          <t>MZ0118</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>MZ0207</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>77.01000000000001</v>
-      </c>
-      <c r="I17" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="J17" t="n">
-        <v>17.24</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>8.52</v>
-      </c>
-      <c r="M17" t="n">
-        <v>37.49</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="inlineStr"/>
-      <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="inlineStr"/>
-      <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="inlineStr"/>
-      <c r="AT17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">June 2024: A school was set on fire by Islamic State-back insurgents during an attack on the village. </t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building </t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>NSA</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>Islamic State</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>Arson</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>School: No Further Details</t>
+        </is>
+      </c>
       <c r="AU17" t="inlineStr"/>
       <c r="AV17" t="inlineStr"/>
       <c r="AW17" t="inlineStr"/>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Inhambane</t>
+          <t>Cabo Delgado</t>
         </is>
       </c>
       <c r="AY17" t="n">
         <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>MZ03</t>
+          <t>MZ01</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>Protests</t>
+          <t>Strategic developments ---- Strategic developments ---- Strategic developments</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>Peaceful protest</t>
+          <t>Looting/property destruction ---- Other ---- Change to group/activity</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>Protesters (Mozambique)</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>Teachers (Mozambique)</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+          <t>Islamic State Mozambique (ISM) ---- Police Forces of Mozambique (1990-) Rapid Intervention Unit ---- Islamic State Mozambique (ISM)</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Civilians (Mozambique) ---- Civilians (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>Health Workers (Mozambique) ---- Journalists (Mozambique)</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>On 6 March 2024, around 30 striking teachers gathered with placards outside Emilia Dausse secondary school in Inhambane (Inhambane, Inhambane) to demand the payment of two years of overtime.</t>
+          <t>Property destruction: On 11 June 2024, Islamist militia attacked Nacoba (Quissanga, Cabo Delgado). The militia looted a health center, destroyed alcoholic beverages, looted tents, and set at least one school on fire. ---- Other: Around 27 August 2024 (as reported), UIR agents detained a Centro de Integridade Publica (CIP) observer accused of being part of an Islamist militia and forced him to delete photos in Quissanga (Quissanga, Cabo Delgado). The CIP correspondent was covering the election campaign and claimed he was photographing posters at the Quissanga-Sede Secondary School because the law prohibits posters at schools. His family intervened to release him. The incident happened in the context of the upcoming October 2024 general election. ---- Movement of forces: Around 19 February 2025 (between 19 - 20 February), ISM militants entered the village and asked residents about aid in Cagembe (Quissanga, Quissanga, Cabo Delgado), causing education workers to flee their posts for safety in Pemba town.</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024-06-11 ---- 2024-08-27 ---- 2025-02-19</t>
         </is>
       </c>
       <c r="BK17" t="inlineStr">
         <is>
-          <t>Inhambane</t>
+          <t>Quissanga</t>
         </is>
       </c>
       <c r="BL17" t="n">
@@ -3083,68 +3069,30 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MZ0305</t>
+          <t>MZ0202</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>MZ0105</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>77.78</v>
-      </c>
-      <c r="I18" t="n">
-        <v>22.22</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>31.31</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
@@ -3172,20 +3120,64 @@
       <c r="AU18" t="inlineStr"/>
       <c r="AV18" t="inlineStr"/>
       <c r="AW18" t="inlineStr"/>
-      <c r="AX18" t="inlineStr"/>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr"/>
-      <c r="BA18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Gaza</t>
+        </is>
+      </c>
+      <c r="AY18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>MZ02</t>
+        </is>
+      </c>
       <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
-      <c r="BG18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>Riots ---- Protests ---- Riots</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>Violent demonstration ---- Peaceful protest ---- Violent demonstration</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>Rioters (Mozambique) ---- Protesters (Mozambique) ---- Rioters (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>Students (Mozambique) ---- Teachers (Mozambique) ---- PODEMOS: Optimistic Party for the Development of Mozambique</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Police Forces of Mozambique (1990-) ---- Police Forces of Mozambique (1990-)</t>
+        </is>
+      </c>
       <c r="BH18" t="inlineStr"/>
-      <c r="BI18" t="inlineStr"/>
-      <c r="BJ18" t="inlineStr"/>
-      <c r="BK18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>On 4 December 2024, students marched along some avenues in Chibuto (Chibuto, Gaza) in support of their teachers demanding payment for their overtime, Students demonstrated in the patio of their secondary school then gathered at a roundabout in the town center. Police officers opened fire against the pupils. A police officer was injured after allegedly being attacked by demonstrators (no further details). He was hospitalized. ---- On 4 December 2024, striking secondary school teachers, singing protest songs and slogans, gathered in Chibuto (Chibuto, Gaza) and prevented secondary school final exams from taking place. They demanded payment for overtime for 2022, 2023 and 2024. This event was part of a collective event taking place simultaneously in at least 5 secondary schools in Gaza province (coded separately). ---- Around 7 December 2024 (between 7 - 8 December), PODEMOS supporters gathered inside the central market in Chibuto (Chibuto, Gaza), following a call by the PODEMOS presidential candidate for an 8-day demonstration against the election results. Police officers attempted to contain the demonstration firing in the air and a civilian was shot dead. This caused the looting and burning of several state institutions, including the courthouse, the registry office, the notary office, the district elections commission, and the education services building. Rioters threw stones at the district infrastructure department, destroying the front of the building. They set on fire a vehicle, stole computers and printers, and they also looted the police commander's official residence. In addition to public institutions, they also looted 6 commercial establishments.</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>2024-12-04 ---- 2024-12-04 ---- 2024-12-07</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>Chibuto</t>
+        </is>
+      </c>
       <c r="BL18" t="n">
         <v>0</v>
       </c>
@@ -3193,68 +3185,30 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MZ0401</t>
+          <t>MZ0205</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>MZ0722</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>67.44</v>
-      </c>
-      <c r="I19" t="n">
-        <v>30.23</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
@@ -3284,7 +3238,7 @@
       <c r="AW19" t="inlineStr"/>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Manica</t>
+          <t>Gaza</t>
         </is>
       </c>
       <c r="AY19" t="n">
@@ -3295,23 +3249,23 @@
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>MZ04</t>
+          <t>MZ02</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr"/>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>Protests</t>
+          <t>Riots</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>Peaceful protest</t>
+          <t>Violent demonstration</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>Protesters (Mozambique)</t>
+          <t>Rioters (Mozambique)</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr"/>
@@ -3319,17 +3273,17 @@
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>Around 18 February 2025 (as reported), demonstrators from Nhampassa invaded (unspecified means) a tourmaline mine in Barue (Nhampassa, Barue, Manica) to demand adherence to an agreement by the Sominha company to provide housing, a school, and a hospital with resources, better roads, and water access.</t>
+          <t>On 17 February 2025, rioters set fire to the FIPAG (Water Supply Investment and Asset Fund) water supply office, and vandalized (damaging computers and documents) the District Education Services and a bakery in Chokwe (Chokwe, Gaza) over demands to reduce the high cost of living and reduce water fees. Elsewhere in Chokwe, they barricaded roads (means unspecified). The demonstrations caused ten schools to close. Free water is a demand called for by Mondlane in post-election demonstrations.</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="BK19" t="inlineStr">
         <is>
-          <t>Barue</t>
+          <t>Chokwe</t>
         </is>
       </c>
       <c r="BL19" t="n">
@@ -3339,68 +3293,30 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MZ0402</t>
+          <t>MZ0206</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>MZ0721</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>94.44</v>
-      </c>
-      <c r="I20" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0.43</v>
-      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
@@ -3428,20 +3344,56 @@
       <c r="AU20" t="inlineStr"/>
       <c r="AV20" t="inlineStr"/>
       <c r="AW20" t="inlineStr"/>
-      <c r="AX20" t="inlineStr"/>
-      <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr"/>
-      <c r="BA20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Gaza</t>
+        </is>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>MZ02</t>
+        </is>
+      </c>
       <c r="BB20" t="inlineStr"/>
-      <c r="BC20" t="inlineStr"/>
-      <c r="BD20" t="inlineStr"/>
-      <c r="BE20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>Protests ---- Protests ---- Protests</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Peaceful protest ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>Protesters (Mozambique) ---- Protesters (Mozambique) ---- Protesters (Mozambique)</t>
+        </is>
+      </c>
       <c r="BF20" t="inlineStr"/>
       <c r="BG20" t="inlineStr"/>
       <c r="BH20" t="inlineStr"/>
-      <c r="BI20" t="inlineStr"/>
-      <c r="BJ20" t="inlineStr"/>
-      <c r="BK20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>On 8 January 2024, residents set up barricades (unspecified) in demonstration in Chongoene (Chongoene, Gaza) against a Chinese mining company's alleged failure to build infrastructure they promised including building a school, health centre, water supply and electricity network and paving a road. ---- On 6 February 2025, protesters blocked the main road to the districts of Mandlakazi, Chibuto and Guija so that drivers could not pass in Bungane (Chongoene, Chongoene, Gaza). They were demanding access to water, energy, and the construction of a secondary school. The district government attempted to convince the protesters to unblock the road without success. ---- On 7 February 2025, protesters, mainly consisting of youth, blocked (means unspecified) the EN102 road in Bairro 5 (Chongoene, Chongoene, Gaza). The demonstration was held against enrolment fees in schools and the lack of access to water and electricity.</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>2024-01-08 ---- 2025-02-06 ---- 2025-02-07</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>Chongoene</t>
+        </is>
+      </c>
       <c r="BL20" t="n">
         <v>0</v>
       </c>
@@ -3449,7 +3401,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MZ0403</t>
+          <t>MZ0207</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -3458,58 +3410,58 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MZ0110</t>
+          <t>MZ0101</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>MZ0107;MZ0110;MZ0403;MZ0711</t>
+          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>89.15000000000001</v>
+        <v>76.36</v>
       </c>
       <c r="I21" t="n">
-        <v>10.08</v>
+        <v>18.18</v>
       </c>
       <c r="J21" t="n">
-        <v>0.78</v>
+        <v>5.45</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>21.43</v>
+        <v>24.72</v>
       </c>
       <c r="M21" t="n">
-        <v>0.78</v>
+        <v>14.54</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
@@ -3538,20 +3490,64 @@
       <c r="AU21" t="inlineStr"/>
       <c r="AV21" t="inlineStr"/>
       <c r="AW21" t="inlineStr"/>
-      <c r="AX21" t="inlineStr"/>
-      <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr"/>
-      <c r="BA21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Gaza</t>
+        </is>
+      </c>
+      <c r="AY21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>MZ02</t>
+        </is>
+      </c>
       <c r="BB21" t="inlineStr"/>
-      <c r="BC21" t="inlineStr"/>
-      <c r="BD21" t="inlineStr"/>
-      <c r="BE21" t="inlineStr"/>
-      <c r="BF21" t="inlineStr"/>
-      <c r="BG21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>Protests ---- Protests</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Excessive force against protesters</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>Protesters (Mozambique) ---- Protesters (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>Teachers (Mozambique) ---- Labor Group (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>Police Forces of Mozambique (1990-)</t>
+        </is>
+      </c>
       <c r="BH21" t="inlineStr"/>
-      <c r="BI21" t="inlineStr"/>
-      <c r="BJ21" t="inlineStr"/>
-      <c r="BK21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>Around 1 February 2024 (as reported), teachers marched in Xai-Xai (Xai-Xai, Gaza) for better working conditions, including the payment of extra hours by the government, and against overcrowded classrooms. ---- On 26 March 2025, over 250 public bus drivers and conductors stopped work and protested in Xai-Xai (Xai-Xai, Gaza) against the installation of a traffic checkpoint in the city. Police shot and killed 1 man while trying to disperse the protesters who were demanding for the deactivation of a traffic checkpoint/inspection post in Potinha neighborhood, claiming that police use it to illegally extort money from drivers. During the demonstrations, traffic on all routes stopped and many schools closed.</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>2024-02-01 ---- 2025-03-26</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>Xai-Xai</t>
+        </is>
+      </c>
       <c r="BL21" t="n">
         <v>0</v>
       </c>
@@ -3559,68 +3555,30 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MZ0410</t>
+          <t>MZ0209</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>MZ0719</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>77.69</v>
-      </c>
-      <c r="I22" t="n">
-        <v>22.31</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>34.42</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
@@ -3648,20 +3606,60 @@
       <c r="AU22" t="inlineStr"/>
       <c r="AV22" t="inlineStr"/>
       <c r="AW22" t="inlineStr"/>
-      <c r="AX22" t="inlineStr"/>
-      <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr"/>
-      <c r="BA22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Gaza</t>
+        </is>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>MZ02</t>
+        </is>
+      </c>
       <c r="BB22" t="inlineStr"/>
-      <c r="BC22" t="inlineStr"/>
-      <c r="BD22" t="inlineStr"/>
-      <c r="BE22" t="inlineStr"/>
-      <c r="BF22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>Protests ---- Protests</t>
+        </is>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>Protesters (Mozambique) ---- Protesters (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>Teachers (Mozambique) ---- Teachers (Mozambique)</t>
+        </is>
+      </c>
       <c r="BG22" t="inlineStr"/>
       <c r="BH22" t="inlineStr"/>
-      <c r="BI22" t="inlineStr"/>
-      <c r="BJ22" t="inlineStr"/>
-      <c r="BK22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>On 4 December 2024, striking secondary school teachers, singing protest songs and slogans, gathered in Licilo (Limpopo, Gaza) and prevented secondary school final exams from taking place. They demanded payment for overtime for 2022, 2023 and 2024. This event was part of a collective event taking place simultaneously in at least 5 secondary schools in Gaza province (coded separately). ---- On 4 December 2024, striking secondary school teachers, singing protest songs and slogans, gathered in Limpopo (Limpopo, Gaza) and prevented secondary school final exams from taking place. They demanded payment for overtime for 2022, 2023 and 2024. This event was part of a collective event taking place simultaneously in at least 5 secondary schools in Gaza province (coded separately).</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>2024-12-04 ---- 2024-12-04</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>Limpopo</t>
+        </is>
+      </c>
       <c r="BL22" t="n">
         <v>0</v>
       </c>
@@ -3669,68 +3667,30 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MZ0701</t>
+          <t>MZ0211</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>MZ0812</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>20</v>
-      </c>
-      <c r="I23" t="n">
-        <v>80</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>123.61</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
@@ -3760,7 +3720,7 @@
       <c r="AW23" t="inlineStr"/>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Gaza</t>
         </is>
       </c>
       <c r="AY23" t="n">
@@ -3771,53 +3731,45 @@
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>MZ07</t>
+          <t>MZ02</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr"/>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>Strategic developments</t>
+          <t>Protests</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Peaceful protest</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>FRELIMO: Liberation Front of Mozambique</t>
+          <t>Protesters (Mozambique)</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>Government of Mozambique (1990-)</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>Civilians (Mozambique)</t>
-        </is>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>Journalists (Mozambique)</t>
-        </is>
-      </c>
+          <t>Teachers (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>Other: On 24 August 2024, an assistant of the Agoche's mayor (FRELIMO member) beat a photojournalist (Paraphato radio) who was filming the start of Frelimo's election campaign at Farlahe Primary School in Inguri neighborhood in Angoche (Angoche, Nampula), and seized his camera. Extent of injuries unknown/not reported. The Community Radio Forum (FORCOM) claimed that the Angoche Mayor and the FRELIMO First Secretary in Angoche were responsible for the attack. Another radio journalist had his material seized on the following day (coded separately). The incident happened in the context of the upcoming October 2024 general election.</t>
+          <t>On 4 December 2024, striking secondary school teachers, singing protest songs and slogans, gathered in Mandlakaze (Mandlakaze, Gaza) and prevented secondary school final exams from taking place. They demanded payment for overtime for 2022, 2023 and 2024. This event was part of a collective event taking place simultaneously in at least 5 secondary schools in Gaza province (coded separately).</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>2024-08-24</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="BK23" t="inlineStr">
         <is>
-          <t>Angoche</t>
+          <t>Mandlakaze</t>
         </is>
       </c>
       <c r="BL23" t="n">
@@ -3827,7 +3779,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MZ0702</t>
+          <t>MZ0301</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -3836,7 +3788,7 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MZ0717</t>
+          <t>MZ0207</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3845,22 +3797,22 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>99.45999999999999</v>
+        <v>77.01000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.54</v>
+        <v>5.75</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>17.24</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>3.95</v>
+        <v>8.52</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>37.49</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3872,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3881,7 +3833,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -3918,64 +3870,56 @@
       <c r="AW24" t="inlineStr"/>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Inhambane</t>
         </is>
       </c>
       <c r="AY24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>MZ07</t>
+          <t>MZ03</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr"/>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>Riots ---- Riots ---- Riots ---- Riots</t>
+          <t>Protests</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>Violent demonstration ---- Violent demonstration ---- Violent demonstration ---- Violent demonstration</t>
+          <t>Peaceful protest</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
-          <t>Rioters (Mozambique) ---- Rioters (Mozambique) ---- Rioters (Mozambique) ---- Rioters (Mozambique)</t>
+          <t>Protesters (Mozambique)</t>
         </is>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>PODEMOS: Optimistic Party for the Development of Mozambique ---- PODEMOS: Optimistic Party for the Development of Mozambique ---- PODEMOS: Optimistic Party for the Development of Mozambique ---- Students (Mozambique)</t>
-        </is>
-      </c>
-      <c r="BG24" t="inlineStr">
-        <is>
-          <t>Police Forces of Mozambique (1990-) ---- Police Forces of Mozambique (1990-) Rapid Intervention Unit ---- Civilians (Mozambique)</t>
-        </is>
-      </c>
-      <c r="BH24" t="inlineStr">
-        <is>
-          <t>Private Security Forces (Mozambique) ---- Police Forces of Mozambique (1990-); Teachers (Mozambique)</t>
-        </is>
-      </c>
+          <t>Teachers (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BG24" t="inlineStr"/>
+      <c r="BH24" t="inlineStr"/>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>Around 7 December 2024 (as reported), PODEMOS supporters attempted to invade the residence of the governor in Nampula (Nampula, Nampula) during a demonstration against election results. Police officers shot a former municipal councilor for education while he was at Cafe Atlantico. Severely injured, he was hospitalized and died on 7 December. ---- Around 15 December 2024 (month of), PODEMOS supporters looted 27 computers and 24 tablets from Namicopo secondary school in Nampula (Nampula, Nampula). They destroyed the computer room, the doors of several compartments and classrooms, and burned documents. The event happened in the context of nationwide demonstrations and unrest against election results. ---- On 24 December 2024, for the second consecutive day, hundreds of PODEMOS supporters blocked (means unspecified) the main roads in several neighborhoods of Nampula (Nampula, Nampula), following a call by the PODEMOS presidential candidate after the announcement on 23 December by the constitutional council of the victory of the FRELIMO party in the presidential, legislative, and provincial elections on 23 December. Commercial establishments were vandalized and looted in the main neighborhoods of Nampula: in the Nasser area, in Muahivire, in Namicopo, and the Mutava Rex area. Several public and private infrastructures were destroyed in Namicopo: hospitals, administrative buildings, police stations, schools, and shopping centers. In Namiepe, rioters destroyed a police station and looted a chicken company. The house of the archdiocese was also looted and hundreds of prisoners at the Northern regional penitentiary establishment attempted to escape. There were clashes (means unspecified) between demonstrators and police officers supported by private security agents. 22 people were killed in the city from 23 December to 26 December (17 arrived dead at the hospital and 4 died upon arrival), and at least 116 were injured and hospitalized, 38 of them with serious conditions. 22 fatalities split across three days and coded as 7 for this event. ---- On 6 March 2025, rioters, suspected supporters of Mondlane (former presidential candidate), barricaded roads with burning tires in Nampula (Nampula, Nampula) during a demonstration against the general election results held in October 2024. At the Waresta Market, Serra da Mesa, Controle, and Angoche Station, rioters threatened local shopkeepers and burned down a vehicle. Students attacked (means unspecified) the school principal and an unspecified number of employees of the Motomoti Elementary School. They also destroyed its administrative block. The school principal had to be hospitalized. Police officers arrested 10 people.</t>
+          <t>On 6 March 2024, around 30 striking teachers gathered with placards outside Emilia Dausse secondary school in Inhambane (Inhambane, Inhambane) to demand the payment of two years of overtime.</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>2024-12-07 ---- 2024-12-15 ---- 2024-12-24 ---- 2025-03-06</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="BK24" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Inhambane</t>
         </is>
       </c>
       <c r="BL24" t="n">
@@ -3985,68 +3929,30 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MZ0703</t>
+          <t>MZ0304</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>MZ0801</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="I25" t="n">
-        <v>14.08</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>51.96</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="U25" t="n">
-        <v>9.629999999999999</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
@@ -4076,56 +3982,52 @@
       <c r="AW25" t="inlineStr"/>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Nampula</t>
+          <t>Inhambane</t>
         </is>
       </c>
       <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
         <v>1</v>
       </c>
-      <c r="AZ25" t="n">
-        <v>3</v>
-      </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>MZ07</t>
+          <t>MZ03</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr"/>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>Violence against civilians ---- Violence against civilians ---- Violence against civilians</t>
+          <t>Riots</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>Attack ---- Attack ---- Attack</t>
+          <t>Violent demonstration</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
-          <t>Islamic State Mozambique (ISM) ---- Islamic State Mozambique (ISM) ---- Islamic State Mozambique (ISM)</t>
+          <t>Rioters (Mozambique)</t>
         </is>
       </c>
       <c r="BF25" t="inlineStr"/>
-      <c r="BG25" t="inlineStr">
-        <is>
-          <t>Civilians (Mozambique) ---- Civilians (Mozambique) ---- Civilians (Mozambique)</t>
-        </is>
-      </c>
+      <c r="BG25" t="inlineStr"/>
       <c r="BH25" t="inlineStr"/>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>On 25 April 2024, Islamist militia attacked Nassua in the district of Erati (location coded to Erati, Erati, Nampula). The Islamic State claimed the attack and the killing of one person, the burning of a church, two 'Christian' schools, three motorcycles, and about 190 houses. ---- On 25 April 2024, Islamist militia attacked Odinepa (Memba, Nampula). Casualties unknown. Products were looted and houses and schools burned. ---- On 26 April 2024, Islamist militia attacked Manika in the district of Erati (location coded to Erati, Erati, Nampula). Casualties unknown. The Islamic State claimed the attack on a 'Christian' village and the burning of a church, a school and more than 30 houses.</t>
+          <t>On 19 February 2025, rioters set fire to a school vehicle, invaded the Frelimo district headquarters, and removed a flagpole in Homoine (Homoine, Inhambane). They were demonstrating against the cost of living, guard fees, and the cost of uniforms. When their demands to return payments were not met they set fire to the school principal's vehicle. They also invaded the Municipal Building, causing the mayor to flee.</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>2024-04-25 ---- 2024-04-25 ---- 2024-04-26</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="BK25" t="inlineStr">
         <is>
-          <t>Erati</t>
+          <t>Homoine</t>
         </is>
       </c>
       <c r="BL25" t="n">
@@ -4135,7 +4037,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MZ0704</t>
+          <t>MZ0305</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -4144,19 +4046,19 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MZ1114</t>
+          <t>MZ0105</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
+          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>68.97</v>
+        <v>77.78</v>
       </c>
       <c r="I26" t="n">
-        <v>31.03</v>
+        <v>22.22</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -4165,7 +4067,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>60.32</v>
+        <v>31.31</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -4180,7 +4082,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -4245,68 +4147,30 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MZ0707</t>
+          <t>MZ0310</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>MZ0710</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>85</v>
-      </c>
-      <c r="I27" t="n">
-        <v>15</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>44.86</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0.45</v>
-      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
@@ -4334,20 +4198,64 @@
       <c r="AU27" t="inlineStr"/>
       <c r="AV27" t="inlineStr"/>
       <c r="AW27" t="inlineStr"/>
-      <c r="AX27" t="inlineStr"/>
-      <c r="AY27" t="inlineStr"/>
-      <c r="AZ27" t="inlineStr"/>
-      <c r="BA27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Inhambane</t>
+        </is>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>MZ03</t>
+        </is>
+      </c>
       <c r="BB27" t="inlineStr"/>
-      <c r="BC27" t="inlineStr"/>
-      <c r="BD27" t="inlineStr"/>
-      <c r="BE27" t="inlineStr"/>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>Riots</t>
+        </is>
+      </c>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>Violent demonstration</t>
+        </is>
+      </c>
+      <c r="BE27" t="inlineStr">
+        <is>
+          <t>Rioters (Mozambique)</t>
+        </is>
+      </c>
       <c r="BF27" t="inlineStr"/>
-      <c r="BG27" t="inlineStr"/>
-      <c r="BH27" t="inlineStr"/>
-      <c r="BI27" t="inlineStr"/>
-      <c r="BJ27" t="inlineStr"/>
-      <c r="BK27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr">
+        <is>
+          <t>Police Forces of Mozambique (1990-)</t>
+        </is>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>FRELIMO: Liberation Front of Mozambique</t>
+        </is>
+      </c>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>On 24 February 2025, rioters barricaded areas with burning tires and destroyed property and infrastructure in multiple locations in Maxixe town (Maxixe, Inhambane). Demonstrations occurred on the EN1 road near the border between Maxixe and Morrumbene districts, by INAS (Institute of Social Action), near the exit toward Homoine, and near the 29 de Setembro secondary school against the cost of living and the lack of basic social services. Rioters destroyed property and infrastructure in the Frelimo headquarters before setting it on fire, and broke windows at the FIPAG (Water Supply Investment and Equity Fund) building. Police intervened with live bullets. There were no casualties.</t>
+        </is>
+      </c>
+      <c r="BJ27" t="inlineStr">
+        <is>
+          <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="BK27" t="inlineStr">
+        <is>
+          <t>Maxixe</t>
+        </is>
+      </c>
       <c r="BL27" t="n">
         <v>0</v>
       </c>
@@ -4355,7 +4263,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MZ0708</t>
+          <t>MZ0401</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -4364,37 +4272,37 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MZ0718</t>
+          <t>MZ0722</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
+          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>95.56</v>
+        <v>67.44</v>
       </c>
       <c r="I28" t="n">
-        <v>4.44</v>
+        <v>30.23</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>22.96</v>
+        <v>47.2</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -4412,7 +4320,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -4444,20 +4352,56 @@
       <c r="AU28" t="inlineStr"/>
       <c r="AV28" t="inlineStr"/>
       <c r="AW28" t="inlineStr"/>
-      <c r="AX28" t="inlineStr"/>
-      <c r="AY28" t="inlineStr"/>
-      <c r="AZ28" t="inlineStr"/>
-      <c r="BA28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Manica</t>
+        </is>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>MZ04</t>
+        </is>
+      </c>
       <c r="BB28" t="inlineStr"/>
-      <c r="BC28" t="inlineStr"/>
-      <c r="BD28" t="inlineStr"/>
-      <c r="BE28" t="inlineStr"/>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>Protests</t>
+        </is>
+      </c>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE28" t="inlineStr">
+        <is>
+          <t>Protesters (Mozambique)</t>
+        </is>
+      </c>
       <c r="BF28" t="inlineStr"/>
       <c r="BG28" t="inlineStr"/>
       <c r="BH28" t="inlineStr"/>
-      <c r="BI28" t="inlineStr"/>
-      <c r="BJ28" t="inlineStr"/>
-      <c r="BK28" t="inlineStr"/>
+      <c r="BI28" t="inlineStr">
+        <is>
+          <t>Around 18 February 2025 (as reported), demonstrators from Nhampassa invaded (unspecified means) a tourmaline mine in Barue (Nhampassa, Barue, Manica) to demand adherence to an agreement by the Sominha company to provide housing, a school, and a hospital with resources, better roads, and water access.</t>
+        </is>
+      </c>
+      <c r="BJ28" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="BK28" t="inlineStr">
+        <is>
+          <t>Barue</t>
+        </is>
+      </c>
       <c r="BL28" t="n">
         <v>0</v>
       </c>
@@ -4465,7 +4409,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MZ0709</t>
+          <t>MZ0402</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -4474,7 +4418,7 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MZ1122</t>
+          <t>MZ0721</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4483,10 +4427,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>87.72</v>
+        <v>94.44</v>
       </c>
       <c r="I29" t="n">
-        <v>12.28</v>
+        <v>5.56</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -4495,7 +4439,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>20.1</v>
+        <v>3.21</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -4525,7 +4469,7 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
@@ -4575,7 +4519,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MZ0710</t>
+          <t>MZ0403</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -4584,31 +4528,31 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MZ0722</t>
+          <t>MZ0110</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
+          <t>MZ0107;MZ0110;MZ0403;MZ0711</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>78.41</v>
+        <v>89.15000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>21.59</v>
+        <v>10.08</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>47.65</v>
+        <v>21.43</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -4620,7 +4564,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -4685,7 +4629,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MZ0711</t>
+          <t>MZ0410</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -4694,43 +4638,43 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MZ0107</t>
+          <t>MZ0719</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MZ0107;MZ0110;MZ0403;MZ0711</t>
+          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>72.41</v>
+        <v>77.69</v>
       </c>
       <c r="I31" t="n">
-        <v>25.29</v>
+        <v>22.31</v>
       </c>
       <c r="J31" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>56.47</v>
+        <v>34.42</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1.45</v>
+        <v>0.43</v>
       </c>
       <c r="P31" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -4742,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
@@ -4795,68 +4739,30 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MZ0712</t>
+          <t>MZ0501</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>MZ0813</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="I32" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>84.08</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0.35</v>
-      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
@@ -4884,20 +4790,68 @@
       <c r="AU32" t="inlineStr"/>
       <c r="AV32" t="inlineStr"/>
       <c r="AW32" t="inlineStr"/>
-      <c r="AX32" t="inlineStr"/>
-      <c r="AY32" t="inlineStr"/>
-      <c r="AZ32" t="inlineStr"/>
-      <c r="BA32" t="inlineStr"/>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Maputo</t>
+        </is>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>MZ05</t>
+        </is>
+      </c>
       <c r="BB32" t="inlineStr"/>
-      <c r="BC32" t="inlineStr"/>
-      <c r="BD32" t="inlineStr"/>
-      <c r="BE32" t="inlineStr"/>
-      <c r="BF32" t="inlineStr"/>
-      <c r="BG32" t="inlineStr"/>
-      <c r="BH32" t="inlineStr"/>
-      <c r="BI32" t="inlineStr"/>
-      <c r="BJ32" t="inlineStr"/>
-      <c r="BK32" t="inlineStr"/>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>Riots ---- Protests</t>
+        </is>
+      </c>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>Violent demonstration ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE32" t="inlineStr">
+        <is>
+          <t>Rioters (Mozambique) ---- Protesters (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BF32" t="inlineStr">
+        <is>
+          <t>PODEMOS: Optimistic Party for the Development of Mozambique ---- Teachers (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BG32" t="inlineStr">
+        <is>
+          <t>Civilians (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>Students (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BI32" t="inlineStr">
+        <is>
+          <t>On 5 November 2024, PODEMOS supporters invaded the Engenheiro Filipe Jacinto Nyusi Secondary School, knocked down the statue of the President of the Republic of Mozambique erected at the school, and circulated through the streets showing the head of the statue in Campoane neighborhood in the district of Boane (location coded to Boane, Maputo), following a call by the PODEMOS presidential candidate for a seven-day national strike. The demonstration was held against police violence during previous PODEMOS-led demonstrations, claims of the assassination of the PODEMOS presidential candidate's legal adviser and legal representative by special forces (coded separately), and what they consider fraudulent general election results. Some students were injured when the school was evacuated. Extent of injuries unknown/not reported. Police officers escorted some students to their houses. The incident happened after the announcement of the final results of the 2024 general election. ---- On 2 December 2024, at the call of the National Teachers' Association (ANAPRO), striking teachers, carrying placards and singing songs, gathered outside Eng. Filipe Jacinto Nyusi, Massaca, Bili Bili and Malangatana Ngwenya secondary schools in Boane (Boane, Maputo) and prevented final exams from taking place. They demanded payment for overtime for 2022, 2023 and 2024. This event was part of a collective event taking place simultaneously in at least 9 secondary schools in Maputo province (coded separately).</t>
+        </is>
+      </c>
+      <c r="BJ32" t="inlineStr">
+        <is>
+          <t>2024-11-05 ---- 2024-12-02</t>
+        </is>
+      </c>
+      <c r="BK32" t="inlineStr">
+        <is>
+          <t>Boane</t>
+        </is>
+      </c>
       <c r="BL32" t="n">
         <v>0</v>
       </c>
@@ -4905,68 +4859,30 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MZ0713</t>
+          <t>MZ0502</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>MZ1106</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>100</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>16.49</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
@@ -4994,20 +4910,68 @@
       <c r="AU33" t="inlineStr"/>
       <c r="AV33" t="inlineStr"/>
       <c r="AW33" t="inlineStr"/>
-      <c r="AX33" t="inlineStr"/>
-      <c r="AY33" t="inlineStr"/>
-      <c r="AZ33" t="inlineStr"/>
-      <c r="BA33" t="inlineStr"/>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Maputo</t>
+        </is>
+      </c>
+      <c r="AY33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>MZ05</t>
+        </is>
+      </c>
       <c r="BB33" t="inlineStr"/>
-      <c r="BC33" t="inlineStr"/>
-      <c r="BD33" t="inlineStr"/>
-      <c r="BE33" t="inlineStr"/>
-      <c r="BF33" t="inlineStr"/>
-      <c r="BG33" t="inlineStr"/>
-      <c r="BH33" t="inlineStr"/>
-      <c r="BI33" t="inlineStr"/>
-      <c r="BJ33" t="inlineStr"/>
-      <c r="BK33" t="inlineStr"/>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Riots ---- Riots ---- Riots ---- Riots ---- Protests ---- Protests ---- Protests</t>
+        </is>
+      </c>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Violent demonstration ---- Violent demonstration ---- Violent demonstration ---- Violent demonstration ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE33" t="inlineStr">
+        <is>
+          <t>Protesters (Mozambique) ---- Protesters (Mozambique) ---- Protesters (Mozambique) ---- Protesters (Mozambique) ---- Protesters (Mozambique) ---- Rioters (Mozambique) ---- Rioters (Mozambique) ---- Rioters (Mozambique) ---- Rioters (Mozambique) ---- Protesters (Mozambique) ---- Protesters (Mozambique) ---- Protesters (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BF33" t="inlineStr">
+        <is>
+          <t>Teachers (Mozambique) ---- Teachers (Mozambique) ---- Teachers (Mozambique) ---- Teachers (Mozambique) ---- Students (Mozambique); Teachers (Mozambique) ---- PODEMOS: Optimistic Party for the Development of Mozambique ---- PODEMOS: Optimistic Party for the Development of Mozambique ---- PODEMOS: Optimistic Party for the Development of Mozambique; Students (Mozambique) ---- Teachers (Mozambique) ---- Teachers (Mozambique) ---- Teachers (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BG33" t="inlineStr">
+        <is>
+          <t>Police Forces of Mozambique (1990-) ---- Police Forces of Mozambique (1990-) ---- Police Forces of Mozambique (1990-)</t>
+        </is>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>Civilians (Mozambique); Police Forces of Mozambique (1990-) Rapid Intervention Unit</t>
+        </is>
+      </c>
+      <c r="BI33" t="inlineStr">
+        <is>
+          <t>On 3 January 2024, teachers marched in Matola (Cidade da Matola, Maputo) demanding the payment of extra hours overdue for more than 13 months and improvements in their working conditions. Protesters blamed the Minister of Education and Human Development. ---- On 26 February 2024, teachers gathered in demonstration and stopped their activities in Matola (Cidade Da Matola, Maputo), demanding the payment of extra hours. Teachers claimed they have not received the payment of extra hours since the end of 2022. ---- On 27 February 2024, teachers gathered in demonstration and stopped their activities in Matola (Cidade Da Matola, Maputo), demanding the payment of extra hours for a second consecutive day. Teachers claimed they have not received the payment of extra hours since the end of 2022. ---- On 3 April 2024, about 60 teachers from the Machava Sede Secondary School gathered in demonstration and stopped their activities in Matola (Cidade Da Matola, Maputo), demanding payment of extra hours. Teachers claimed they have not received the payment of extra hours since 2022 and decided to go on strike for seven days. ---- On 4 April 2024, teachers from the Community School Daejo Chiele gathered in demonstration and stopped their activities in Matola (Cidade Da Matola, Maputo) demanding payment of extra hours. Students also gathered in support of their teachers. Teachers claimed they have not received the payment of extra hours since 2022, following a seven-day strike which started the day before in the city. ---- Around 27 August 2024 (as reported), residents barricaded with tires on fire a road in Godlhoza neighborhood in Matola (Cidade da Matola Maputo), demanding electricity supply and improvements to the road that gives access to the neighborhood. Residents also complained about the lack of classrooms and the existence of a corral close to a local school. ---- On 24 October 2024, PODEMOS staged a demonstration in Matola (Cidade da Matola, Maputo), following a call by the PODEMOS presidential candidate for a two-day national strike. The demonstration was held against police violence during previous PODEMOS-led demonstrations, claims of the assassination of the PODEMOS presidential candidate's legal adviser and legal representative by special forces (coded separately), and what they consider fraudulent general election results. Rioters barricaded National Circular Road with burning tires, attacked a police subunit, set fire to an ATM machine at Macahava-Baiao, burned a primary school in Intaka, marched, looted a bottle store, a cell phone store, and a supermarket, and robbed meat and alcoholic beverages. Rioters burned tires, broke bottles, and threw stones in the middle of the roads in the neighborhoods T3, Zona Verde, Machava, Ndlavela, and Nkobe. Rioters also burned tires and left bottle fragments at the Matola toll. Police forces intervened (means unspecified). Shops and schools were closed. According to the spokesperson for the General Command of the police, during the 24 October demonstrations, across the country, at least 20 people were injured, and 371 were detained by police forces. The incident happened after the announcement of the final results of the 2024 general election. ---- On 7 November 2024, thousands of PODEMOS supporters staged a demonstration in Matola (Cidade da Matola, Maputo), following a call by the PODEMOS presidential candidate for a seven-day national strike and demonstrations. The demonstrations were held against police violence during previous PODEMOS-led demonstrations, claims of the assassination of the PODEMOS presidential candidate's legal adviser and legal representative by special forces (coded separately), and what they consider fraudulent general election results. Rioters blocked (means unspecified) National Road Number 4, threw stones at police officers, looted containers, installed tolls and demanded people to pay money to access a road, threw stones at the car windows of those who refused to pay, invaded, looted, and destroyed the windows of Matola Supermarket, destroyed (means unspecified) the windows of an ambulance, and attempted to march to Maputo. Police officers and UIR agents intervened firing tear gas and live bullets at demonstrators and into people's homes. 2 people died and 32 were injured. Armored cars were deployed. Establishments, including educational institutions and gas stations, were closed. Thousands attempted to march from Matola, Ponta do Ouro, and Boane to Maputo (coded separately). ---- On 15 November 2024, thousands of PODEMOS staged a demonstration in Matola (Cidade da Matola), following the killing of a 14-year-old during demonstrations on the previous day (coded separately), and following a call by the PODEMOS presidential candidate for a three-day national strike. The demonstration was held against police violence during previous PODEMOS-led demonstrations, claims of the assassination of the PODEMOS presidential candidate's legal adviser and legal representative by special forces (coded separately), and what they consider fraudulent general election results. Rioters marched to a police station, barricaded roads with burning tires, invaded and looted a supermarket in the Liberdade neighborhood, banged pots, pans, and other metal objects, and played drums, horns, whistles, and vuvuzelas from 9 pm to 10 pm, some from their homes, while others took to the streets. Police intervened firing tear gas. Injuries unknown/not reported. At least seven demonstrators died and seven were injured and admitted to a hospital, including an 18-year-old student, in a hit-and-run on the N4 highway in the Malhampsene neighborhood, in the Texlon area of Matola. One victim had injuries in his leg, left arm, and head, another victim had injuries in his leg, back, head, and face, and lost some teeth. The 18-year-old student had serious injuries in one leg. ---- On 2 December 2024, at the call of the National Teachers' Association (ANAPRO), striking teachers, carrying placards and singing songs, gathered outside Liberdade secondary school in Matola (Cidade Da Matola, Maputo) and prevented final exams from taking place. They demanded payment for overtime for 2022, 2023 and 2024. This event was part of a collective event taking place simultaneously in at least 9 secondary schools in Maputo province (coded separately). ---- On 2 December 2024, at the call of the National Teachers' Association (ANAPRO), striking teachers, carrying placards and singing songs, gathered outside Matlemele, Mahulaze and Sao Damaso secondary schools, in Machava (Cidade Da Matola, Maputo) and prevented final exams from taking place. They demanded payment for overtime for 2022, 2023 and 2024. This event was part of a collective event taking place simultaneously in at least 9 secondary schools in Maputo province (coded separately). ---- On 23 January 2025, striking teachers of Khongolete Secondary School, with pamphlets, protested in Matola (Cidade Da Matola, Maputo), demanding the payment of overtime for 3 years.</t>
+        </is>
+      </c>
+      <c r="BJ33" t="inlineStr">
+        <is>
+          <t>2024-01-03 ---- 2024-02-26 ---- 2024-02-27 ---- 2024-04-03 ---- 2024-04-04 ---- 2024-08-27 ---- 2024-10-24 ---- 2024-11-07 ---- 2024-11-15 ---- 2024-12-02 ---- 2024-12-02 ---- 2025-01-23</t>
+        </is>
+      </c>
+      <c r="BK33" t="inlineStr">
+        <is>
+          <t>Cidade Da Matola</t>
+        </is>
+      </c>
       <c r="BL33" t="n">
         <v>0</v>
       </c>
@@ -5015,68 +4979,30 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MZ0715</t>
+          <t>MZ0601</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>MZ0913</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>MZ0715;MZ0907;MZ0913</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>81.31</v>
-      </c>
-      <c r="I34" t="n">
-        <v>18.69</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>28.33</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
@@ -5104,20 +5030,68 @@
       <c r="AU34" t="inlineStr"/>
       <c r="AV34" t="inlineStr"/>
       <c r="AW34" t="inlineStr"/>
-      <c r="AX34" t="inlineStr"/>
-      <c r="AY34" t="inlineStr"/>
-      <c r="AZ34" t="inlineStr"/>
-      <c r="BA34" t="inlineStr"/>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Maputo City</t>
+        </is>
+      </c>
+      <c r="AY34" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>28</v>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>MZ06</t>
+        </is>
+      </c>
       <c r="BB34" t="inlineStr"/>
-      <c r="BC34" t="inlineStr"/>
-      <c r="BD34" t="inlineStr"/>
-      <c r="BE34" t="inlineStr"/>
-      <c r="BF34" t="inlineStr"/>
-      <c r="BG34" t="inlineStr"/>
-      <c r="BH34" t="inlineStr"/>
-      <c r="BI34" t="inlineStr"/>
-      <c r="BJ34" t="inlineStr"/>
-      <c r="BK34" t="inlineStr"/>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>Protests ---- Protests ---- Riots ---- Riots ---- Riots ---- Riots ---- Riots ---- Strategic developments ---- Riots ---- Riots ---- Riots ---- Protests ---- Violence against civilians ---- Riots ---- Protests ---- Violence against civilians ---- Riots ---- Riots ---- Riots ---- Riots ---- Protests ---- Riots ---- Riots ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests</t>
+        </is>
+      </c>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Peaceful protest ---- Mob violence ---- Violent demonstration ---- Violent demonstration ---- Violent demonstration ---- Violent demonstration ---- Other ---- Violent demonstration ---- Violent demonstration ---- Violent demonstration ---- Excessive force against protesters ---- Attack ---- Violent demonstration ---- Protest with intervention ---- Attack ---- Violent demonstration ---- Violent demonstration ---- Violent demonstration ---- Violent demonstration ---- Peaceful protest ---- Violent demonstration ---- Violent demonstration ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Excessive force against protesters ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE34" t="inlineStr">
+        <is>
+          <t>Protesters (Mozambique) ---- Protesters (Mozambique) ---- Rioters (Mozambique) ---- Rioters (Mozambique) ---- Rioters (Mozambique) ---- Rioters (Mozambique) ---- Rioters (Mozambique) ---- Protesters (Mozambique) ---- Rioters (Mozambique) ---- Rioters (Mozambique) ---- Rioters (Mozambique) ---- Protesters (Mozambique) ---- Police Forces of Mozambique (1990-) National Criminal Investigation Service (SERNIC) ---- Rioters (Mozambique) ---- Protesters (Mozambique) ---- Police Forces of Mozambique (1990-) ---- Rioters (Mozambique) ---- Rioters (Mozambique) ---- Rioters (Mozambique) ---- Rioters (Mozambique) ---- Protesters (Mozambique) ---- Rioters (Mozambique) ---- Rioters (Mozambique) ---- Protesters (Mozambique) ---- Protesters (Mozambique) ---- Protesters (Mozambique) ---- Protesters (Mozambique) ---- Protesters (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BF34" t="inlineStr">
+        <is>
+          <t>Teachers (Mozambique) ---- Students (Mozambique) ---- Journalists (Mozambique); PODEMOS: Optimistic Party for the Development of Mozambique; Civilians (Mozambique) ---- PODEMOS: Optimistic Party for the Development of Mozambique; Civilians (Mozambique) ---- Civilians (Mozambique); PODEMOS: Optimistic Party for the Development of Mozambique ---- Students (Mozambique); PODEMOS: Optimistic Party for the Development of Mozambique ---- MDM: Mozambique Democratic Movement; ND: New Democracy; PODEMOS: Optimistic Party for the Development of Mozambique ---- PODEMOS: Optimistic Party for the Development of Mozambique; Students (Mozambique); Civilians (Mozambique) ---- Civilians (Mozambique); PODEMOS: Optimistic Party for the Development of Mozambique; Students (Mozambique) ---- Civilians (Mozambique); PODEMOS: Optimistic Party for the Development of Mozambique; Students (Mozambique) ---- Health Workers (Mozambique); Labor Group (Mozambique); PODEMOS: Optimistic Party for the Development of Mozambique; Students (Mozambique) ---- PODEMOS: Optimistic Party for the Development of Mozambique ---- Teachers (Mozambique) ---- PODEMOS: Optimistic Party for the Development of Mozambique; Students (Mozambique) ---- PODEMOS: Optimistic Party for the Development of Mozambique; Students (Mozambique) ---- PODEMOS: Optimistic Party for the Development of Mozambique; Students (Mozambique) ---- PODEMOS: Optimistic Party for the Development of Mozambique; Students (Mozambique) ---- Teachers (Mozambique) ---- PODEMOS: Optimistic Party for the Development of Mozambique ---- PODEMOS: Optimistic Party for the Development of Mozambique ---- Labor Group (Mozambique); Teachers (Mozambique) ---- PODEMOS: Optimistic Party for the Development of Mozambique ---- Teachers (Mozambique) ---- Students (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BG34" t="inlineStr">
+        <is>
+          <t>Police Forces of Mozambique (1990-) ---- Police Forces of Mozambique (1990-) ---- Police Forces of Mozambique (1990-) ---- Police Forces of Mozambique (1990-) ---- Police Forces of Mozambique (1990-) ---- Police Forces of Mozambique (1990-) ---- Police Forces of Mozambique (1990-) ---- Police Forces of Mozambique (1990-) ---- Police Forces of Mozambique (1990-) ---- Civilians (Mozambique) ---- Police Forces of Mozambique (1990-) ---- Police Forces of Mozambique (1990-) ---- Civilians (Mozambique) ---- Civilians (Mozambique) ---- Civilians (Mozambique) ---- Civilians (Mozambique) ---- Civilians (Mozambique) ---- Police Forces of Mozambique (1990-) ---- Police Forces of Mozambique (1990-) Rapid Intervention Unit</t>
+        </is>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>Police Forces of Mozambique (1990-) Rapid Intervention Unit ---- Police Forces of Mozambique (1990-) Rapid Intervention Unit; Civilians (Mozambique) ---- Civilians (Mozambique); Police Forces of Mozambique (1990-) Rapid Intervention Unit ---- Police Forces of Mozambique (1990-) Rapid Intervention Unit ---- Police Forces of Mozambique (1990-) Rapid Intervention Unit ---- Police Forces of Mozambique (1990-) Rapid Intervention Unit ---- Students (Mozambique) ---- Students (Mozambique) ---- Labor Group (Mozambique) ---- Labor Group (Mozambique) ---- Labor Group (Mozambique) ---- Labor Group (Mozambique) ---- Police Forces of Mozambique (1990-) Rapid Intervention Unit</t>
+        </is>
+      </c>
+      <c r="BI34" t="inlineStr">
+        <is>
+          <t>On 29 January 2024, teachers protested in Maputo (Maputo City, Maputo) for better working conditions, including the payment of extra hours, and against overcrowded classrooms. ---- On 5 February 2024, a group of about 40 students camped in demonstration outside the Institute of Scholarships (IBE) in Maputo (Maputo City - Kampfumo, Maputo), for the fulfilment of an agreement between IBE and the University of International Integration of Afro-Brazilian Lusophony (Unilab) to finance scholarships in Brazil. The students camped outside IBE for almost a week. ---- On 9 October 2024, a mob invaded a polling station and set a tire on fire at the Secondary School of Mubukwana in Maputo (Maputo City - Kamubukwana, Maputo) following claims of ballot stuffing due to a power outage. Police officers intervened firing shots in the air to disperse the crowd. One man was shot and admitted to a hospital. Four people were arrested. The incident happened during the 2024 general election. ---- On 21 October 2024, between 300 and 500 PODEMOS supporters gathered to march in a demonstration at the OMM Square in Maputo (Maputo City - Kampfumo, Maputo), following a call by the PODEMOS presidential candidate for a national strike. The demonstration was held over claims of the assassination of the PODEMOS presidential candidate's legal adviser and legal representative by special forces (coded separately), and what they consider fraudulent general election results. Police forces and members of the Rapid Intervention Unit (UIR) positioned at the square aborted the start of the march firing tear gas, which led to clashes. PODEMOS supporters burned FRELIMO flags, threw stones and bottles at police officers, vandalized (some using machetes) vehicles, barricaded roads with burning tires, including the road leading to the South African border, knocked down street lighting poles and advertising panels in various neighborhoods, destroyed a vehicle from the National Public Safety Service, and overturned a police armored vehicle. Police used armored vehicles, and dog units, and fired rubber bullets, live bullets in the air, and tear gas (a police helicopter also launched tear gas) at people. Police fired tear gas at journalists and the PODEMOS presidential candidate, while he was briefing a group of journalists. At least 1 person died, a young man who was shot by police officers while leaving his house and died in the neighborhood of Urbanizacao. At least 16 people were injured, including at least three journalists, with five being seriously injured and admitted to a hospital with fractures and trauma. Two people were shot and admitted to Hospital General Polana Calico, and an unknown number of people were shot and injured and admitted to Hospital Geral de Mavalane. Maputo Central Hospital claimed 16 people were admitted to the hospital. Officers detained at least 6 people (conflicting reports ranging between 6 and 30), and seven were later released in Maputo. PODEMOS presidential candidate claimed that SERNIC members fired shots on the public highway. He fled the area after officers threw tear gas and claimed that 95% of activities were shut down in Mozambique. Some schools and shops were closed. The government denied that police forces fired tear gas at journalists, only at rioters. There were demonstrations in Moatize, Beira, Quelimane, Nacala, Tete, and Pemba (coded separately). The incident happened during the vote counting of the 2024 general election. ---- On 24 October 2024, hundreds of PODEMOS supporters staged a demonstration in Maputo (Maputo City, Maputo), following a call by the PODEMOS presidential candidate for a two-day national strike. The demonstration was held against police violence during previous PODEMOS-led demonstrations, claims of the assassination of the PODEMOS presidential candidate's legal adviser and legal representative by special forces (coded separately), and what they consider fraudulent general election results. Rioters barricaded roads with burning tires and garbage containers, blocked the Maputo Circular Road (means unspecified), burned four vehicles, sofas, and other objects, knocked down lighting poles, advertising panels, and garbage containers, threw stones and other projectiles at police officers, threw stones at cars returning from South Africa, damaging at least three cars, vandalized shops, a wholesale refill container, looted property, and destroyed a traffic light in Hulene neighborhood (coded seaprately). Police officers and Rapid Intervention Unit members intervened firing shots and tear gas, barricading roads with burning tires, using dog units, armored vehicles, and hovering a helicopter above the area. At least three people died (split across 2 events, 2 fatalities coded here). 18 people were admitted to Maputo Central Hospital. One woman was shot and seriously injured. A housewife had her house invaded by tear gas and had to run away from a tear gas bullet. Another bullet hit the children who were inside the home. Injuries unknown/not reported. Passengers escaped unharmed from the four vehicles burned by rioters. Police set up a security perimeter on Joaquim Chissano Avenue. Many shops, banks, and schools closed. Violence spread to Ressano Garcia (coded separately). Police officers escorted cars traveling between Maputo and Matola. Police looted a shop. Police detained more than 100 people in almost all neighborhoods of the province and city of Maputo. According to the spokesperson for the General Command of the police, during the 24 October demonstrations, across the country, at least 20 people were injured, and 371 were detained by police forces. The incident happened after the announcement of the final results of the 2024 general election. ---- On 24 October 2024, hundreds of PODEMOS supporters staged a demonstration in Maputo (Maputo City, Maputo), following a call by the PODEMOS presidential candidate for a two-day national strike. The demonstration was held against police violence during previous PODEMOS-led demonstrations, claims of the assassination of the PODEMOS presidential candidate's legal adviser and legal representative by special forces (coded separately), and what they consider fraudulent general election results. Rioters barricaded roads with burning tires and garbage containers, blocked the Maputo Circular Road (means unspecified), burned four vehicles, sofas, and other objects, knocked down lighting poles, advertising panels, and garbage containers, threw stones and other projectiles at police officers, threw stones at cars returning from South Africa, damaging at least three cars, vandalized shops, a wholesale refill container, looted property, and destroyed a traffic light in Hulene neighborhood (Maputo City - Kamavota, Maputo). Police officers and Rapid Intervention Unit members intervened firing shots and tear gas, barricading roads with burning tires, using dog units, armored vehicles, and hovering a helicopter above the area. At least three people died (split across 2 events, 1 fatality coded here). 18 people were admitted to Maputo Central Hospital. One woman was shot and seriously injured. A housewife had her house invaded by tear gas and had to run away from a tear gas bullet. Another bullet hit the children who were inside the home. Injuries unknown/not reported. Passengers escaped unharmed from the four vehicles burned by rioters. Police set up a security perimeter on Joaquim Chissano Avenue. Many shops, banks, and schools closed. Violence spread to Ressano Garcia (coded separately). Police officers escorted cars traveling between Maputo and Matola. Police looted a shop. Police detained more than 100 people in almost all neighborhoods of the province and city of Maputo. According to the spokesperson for the General Command of the police, during the 24 October demonstrations, across the country, at least 20 people were injured, and 371 were detained by police forces. The incident happened after the announcement of the final results of the 2024 general election. ---- On 25 October 2024, for a second consecutive day of demonstrations, a dozen students marched, and PODEMOS supporters burned tires, and littered the street with broken glass and other debris in Maputo (Maputo City, Maputo), following a call by the PODEMOS presidential candidate for a two-day national strike. The demonstration was held against police violence during previous PODEMOS-led demonstrations, claims of the assassination of the PODEMOS presidential candidate's legal adviser and legal representative by special forces (coded separately), and what they consider fraudulent general election results. Police officers escorted the students. A general internet outage among various mobile operators marked the day. Shops and institutions were closed. The incident happened after the announcement of the final results of the 2024 general election. ---- Strikes: On 31 October 2024, public and private institutions closed in various cities in Mozambique, including Maputo (Maputo City, Maputo), Beira, Matola, Nampula, Chimoio, and Pebane, following a call by the PODEMOS presidential candidate for a seven-day national strike. Demonstrations were held in Tete, Beira, Maputo, and Pebane (coded separately). The PODEMOS presidential candidate called for demonstrations at local CNE offices and the headquarters of the Mozambique Liberation Front. Public and private institutions closed, including private schools, banks, and shops. The Mozambican government restricted access to social media overnight for a second time in a week (coded separately) throughout the country to contain demonstrations. Members of about 40 opposition political parties, including PODEMOS, MDM, and New Democracy, met and announced an alliance to contest the results. The alliance signed up for the week of demonstrations and promised to lead demonstrations at the grassroots level. A member of PODEMOS declared that parallel counts carried out by the opposition parties pointed to the conviction that the counting process deprived the rights of all competing parties. The opposition alliance demanded a forensic audit of the elections and for the electoral authorities to be held to account for taking part in fraud. RENAMO was not present. The Constitutional Council of Mozambique ordered the National Elections Commission to hand over the minutes and results sheets (editais) of the vote counts carried out at polling stations and district elections commissions in six provinces, and the city of Maputo. Mozambican businesspeople estimated losses of 3,000 million meticais (43.2 million euros) in the three days of demonstrations and strike, which left 1,200 unemployed. ---- On 4 November 2024, for the fifth consecutive day, hundreds of PODEMOS supporters, students, and members of political parties (unspecified) staged a demonstration in Maputo (Maputo City, Maputo), following a call by the PODEMOS presidential candidate for a seven-day national strike and demonstrations. The demonstrations were held against police violence during previous PODEMOS-led demonstrations, claims of the assassination of the PODEMOS presidential candidate's legal adviser and legal representative by special forces (coded separately), and what they consider fraudulent general election results. Rioters burned tires on some roads and threw stones and other objects at police officers after they threw tear gas at demonstrators. More than 30 agents from the Rapid Intervention Unit (UIR), two BTRs, and at least five police patrol vehicles were deployed, blocking the march less than 2 km from the Presidency. Police officers intervened firing tear gas and live bullets, at least two people were shot and injured, including a student hit with tear gas in Magoanine B while walking home from school (coded separately). Center for Public Integrity (CIP) claimed police killed three demonstrators in Maputo on 4 and 3 October (coded separately). 3 fatalities split across two events in Maputo and coded as 1 for this event. Conflicting reports ranging between one and five people, including three children. An unknown number of demonstrators were admitted to a hospital. At night, students from Eduardo Mondlane University and other residents banged pots and pans for two hours (coded separately). Rapid Intervention Unit (UIR) agents fired tear gas onto the asphalt and the balconies of the buildings. Injuries unknown/not reported. Internet access was restricted. ---- On 4 November 2024, for the fifth consecutive day, hundreds of PODEMOS supporters, students, and members of political parties (unspecified) staged a demonstration in Maputo (coded separately), following a call by the PODEMOS presidential candidate for a seven-day national strike and demonstrations. The demonstrations were held against police violence during previous PODEMOS-led demonstrations, claims of the assassination of the PODEMOS presidential candidate's legal adviser and legal representative by special forces (coded separately), and what they consider fraudulent general election results. Rioters burned tires on some roads and threw stones and other objects at police officers after they threw tear gas at demonstrators. More than 30 agents from the Rapid Intervention Unit (UIR), two BTRs, and at least five police patrol vehicles were deployed, blocking the march less than 2 km from the Presidency. Police officers intervened firing tear gas and live bullets, at least two people were shot and injured, including a student hit with tear gas in Magoanine B while walking home from school (coded separately). Center for Public Integrity (CIP) claimed police killed three demonstrators in Maputo on 4 and 3 October (coded separately). 3 fatalities split across two events in Maputo and coded as 0 for this event. Conflicting reports ranging between one and five people, including three children. An unknown number of demonstrators were admitted to a hospital. At night, students from Eduardo Mondlane University and other residents banged pots and pans for two hours in Maputo City - Kampfumo (Maputo City). Rapid Intervention Unit (UIR) agents fired tear gas onto the asphalt and the balconies of the buildings. Injuries unknown/not reported. Internet access was restricted. ---- On 4 November 2024, for the fifth consecutive day, hundreds of PODEMOS supporters, students, and members of political parties (unspecified) staged a demonstration in Maputo (coded separately), following a call by the PODEMOS presidential candidate for a seven-day national strike and demonstrations. The demonstrations were held against police violence during previous PODEMOS-led demonstrations, claims of the assassination of the PODEMOS presidential candidate's legal adviser and legal representative by special forces (coded separately), and what they consider fraudulent general election results. Rioters burned tires on some roads and threw stones and other objects at police officers after they threw tear gas at demonstrators. More than 30 agents from the Rapid Intervention Unit (UIR), two BTRs, and at least five police patrol vehicles were deployed, blocking the march less than 2 km from the Presidency. Police officers intervened firing tear gas and live bullets, at least two people were shot and injured, including a student hit with tear gas in Magoanine B while walking home from school (Maputo City - Kamubukwana, Maputo city). Center for Public Integrity (CIP) claimed police killed three demonstrators in Maputo on 4 and 3 October (coded separately). 3 fatalities split across two events in Maputo and coded as 0 for this event. Conflicting reports ranging between one and five people, including three children. An unknown number of demonstrators were admitted to a hospital. At night, students from Eduardo Mondlane University and other residents banged pots and pans for two hours. Rapid Intervention Unit (UIR) agents fired tear gas onto the asphalt and the balconies of the buildings. Injuries unknown/not reported. Internet access was restricted. ---- On 5 November 2024, for the sixth consecutive day of demonstrations, a few hundred Mozambican health workers, including doctors, stretcher-bearers, drivers, students, and members of the Mozambican Medical Association, marched in Maputo (Maputo City, Maputo) against recent violence, following a call by the PODEMOS presidential candidate for a seven-day national strike and demonstrations. The demonstrations were held to protest police violence during previous PODEMOS-led demonstrations, claims of the assassination of the PODEMOS presidential candidate's legal adviser and legal representative by special forces (coded separately), and what they consider fraudulent general election results. The Center for Public Integrity (CIP) claimed police killed 5 people in Maputo and Matola (coded separately) during the demonstrations on 5 November. 5 fatalities split across 2 locations and coded as 3 for this event. Police also blocked (means unspecified) roads. The government restricted Internet access for a second consecutive day. ---- Around 13 November 2024 (week of), SERNIC agents kidnapped a student from Eduardo Mondlane University on Vladimir Lenine Avenue in Maputo (Maputo City - Kamaxaquene, Maputo). The kidnappers, driving a black car, blindfolded, gagged, and took the student to a residence. The agents knew the student was a protester at the university residence and interrogated and tortured him (means unspecified). Extent of injuries unknown/not reported. The student was later released. ---- On 15 November 2024, thousands of PODEMOS supporters staged a demonstration in Maputo City - Kamubukwana (Maputo City, Maputo), following a call by the PODEMOS presidential candidate for a three-day national strike. The demonstration was held against police violence during previous PODEMOS-led demonstrations, claims of the assassination of the PODEMOS presidential candidate's legal adviser and legal representative by special forces (coded separately), and what they consider fraudulent general election results. Rioters barricaded with burning tires a road in the Zimpeto neighborhood near the National Stadium after a soccer match, demanded the payment of a toll to let drivers pass on some roads, set fire to the pedagogical sectors of the Bagamoio Primary School and the Mozambican Heroes Secondary School in the Bagamoio neighborhood, looted drivers, threw stones at drivers, broke the windows of dozens of vehicles mostly in the National Road Number 4 and Maputo Circular, and invaded and looted a warehouse selling alcoholic beverages in the neighborhood Magoanine C. Police intervened firing tears gas and live bullets, killing and injuring an unknown number of demonstrators. Unspecified fatalities coded as 3. Thousands banged pots, pans, and other metal objects, and played drums, horns, whistles, and vuvuzelas, at home and on the streets in Maputo, Boane, Marracuene, and Matola (coded separately). ---- On 16 November 2024, between dozens and several hundred teachers, organized by the National Association of Teachers of Mozambique, marched from the Teachers' Garden in the center of Maputo (Maputo City, Maputo), demanding the government to pay overtime for 22 months in arrears and provide better salary conditions, and adjustments to the Single Salary Table (TSU). Police intervened by firing tear gas and blocking the march close to the Maputo Commercial Institute. Injuries unknown/not reported. Police detained five teachers while they were concentrating on the march. Police allowed the march after negotiations and escorted protesters. ---- Around 18 November 2024 (as reported), an unidentified group, driving a black car (likely Police Force, due to contextual notes) abducted a student from the Eduardo Mondlane university in Maputo (Maputo City - Kampfumo, Maputo City). He was blindfolded, gagged, 'tortured' and held captive for 24 hours by Mozambique's National Criminal Investigation Service (SERNIC). The student was one of the protesters of PODEMOS-led demonstrations. No further on injuries. ---- On 21 November 2024, at midday, PODEMOS supporters and students from the Technical University of Mozambique (UDM) staged a demonstration in Maputo City, following a call by the PODEMOS presidential candidate for a three-day national strike. The demonstration was held as part of phase four of PODEMOS-led demonstrations, against police violence during previous PODEMOS-led demonstrations, to mourn the deaths of about 50 people who were shot by police officers. Rioters wearing black blocked (means unspecified) the access to the parking place of Zimpeto market (coded separately), forced drivers to stop their vehicles and honk, threw stones (victims unspecified), broke the windows of some establishments, and stole the hair prosthetics from one a saleswomen who was in front of a store. Demonstrators wearing black and holding flags and PODEMOS banners occupied National Road Number 4, Eduardo Mondlane (coded separately), Filipe Magaia (Coded separately), People's War, September 25th, and Maputo's Circular avenues, played whistles, while some drivers stopped their cars at midday and honked their horns for 15 minutes, following the instructions of the PODEMOS presidential candidate. Businesses closed in the city center. ---- On 21 November 2024, at midday, PODEMOS supporters and students from the Technical University of Mozambique (UDM) staged a demonstration in Maputo City, following a call by the PODEMOS presidential candidate for a three-day national strike. The demonstration was held as part of phase four of PODEMOS-led demonstrations, against police violence during previous PODEMOS-led demonstrations, to mourn the deaths of about 50 people who were shot by police officers. Rioters wearing black blocked (means unspecified) the access to the parking place of Zimpeto market (coded separately), forced drivers to stop their vehicles and honk, threw stones (victims unspecified), broke the windows of some establishments, and stole the hair prosthetics from one a saleswomen who was in front of a store. Demonstrators wearing black and holding flags and PODEMOS banners occupied National Road Number 4, Eduardo Mondlane (Maputo City - Kamavota), Filipe Magaia (Coded separately), People's War, September 25th, and Maputo's Circular avenues, played whistles, while some drivers stopped their cars at midday and honked their horns for 15 minutes, following the instructions of the PODEMOS presidential candidate. Businesses closed in the city center. ---- On 21 November 2024, at midday, PODEMOS supporters and students from the Technical University of Mozambique (UDM) staged a demonstration in Maputo City, following a call by the PODEMOS presidential candidate for a three-day national strike. The demonstration was held as part of phase four of PODEMOS-led demonstrations, against police violence during previous PODEMOS-led demonstrations, to mourn the deaths of about 50 people who were shot by police officers. Rioters wearing black blocked (means unspecified) the access to the parking place of Zimpeto market (Maputo City - Kampfumo), forced drivers to stop their vehicles and honk, threw stones (victims unspecified), broke the windows of some establishments, and stole the hair prosthetics from one a saleswomen who was in front of a store. Demonstrators wearing black and holding flags and PODEMOS banners occupied National Road Number 4, Eduardo Mondlane (coded separately), Filipe Magaia (Coded separately), People's War, September 25th, and Maputo's Circular avenues, played whistles, while some drivers stopped their cars at midday and honked their horns for 15 minutes, following the instructions of the PODEMOS presidential candidate. Businesses closed in the city center. ---- On 21 November 2024, at midday, PODEMOS supporters and students from the Technical University of Mozambique (UDM) staged a demonstration in Maputo City, following a call by the PODEMOS presidential candidate for a three-day national strike. The demonstration was held as part of phase four of PODEMOS-led demonstrations, against police violence during previous PODEMOS-led demonstrations, to mourn the deaths of about 50 people who were shot by police officers. Rioters wearing black blocked (means unspecified) the access to the parking place of Zimpeto market (coded separately), forced drivers to stop their vehicles and honk, threw stones (victims unspecified), broke the windows of some establishments, and stole the hair prosthetics from one a saleswomen who was in front of a store. Demonstrators wearing black and holding flags and PODEMOS banners occupied National Road Number 4, Eduardo Mondlane (coded separately), Filipe Magaia (Maputo City - Kamubukwana), People's War, September 25th, and Maputo's Circular avenues, played whistles, while some drivers stopped their cars at midday and honked their horns for 15 minutes, following the instructions of the PODEMOS presidential candidate. Businesses closed in the city center. ---- On 2 December 2024, at the call of the National Teachers' Association (ANAPRO), striking teachers, carrying placards and singing songs, gathered outside the Unidade 2 Primary School in Maputo (Maputo City - Kamubukwana, Maputo City) and prevented secondary school final exams from taking place. They demanded payment for overtime for 2022, 2023 and 2024. This event was part of a collective event taking place simultaneously in at least 9 secondary schools in Maputo province (coded separately). ---- On 23 December 2024, hundreds of PODEMOS supporters barricaded several roads with power poles, boulders, and burning tires in Maputo City including in Maputo City - Kamubukwana (Maputo City), following a call by the PODEMOS presidential candidate after the announcement by the Constitutional Council of the victory of the FRELIMO party in the presidential, legislative and provincial elections. Rioters set on fire the BIM counter in the 25 de Junho A neighborhood and destroyed the Maputo toll booths, the Matola-Gare and Cumbeza toll booths on the Maputo ring road. In the George Dimitrov neighborhood, a BCI counter was set on fire and a Handling warehouse was looted. In the Inhagoia A neighborhood, residents set fire to the police station and the neighborhood secretariat, including the FRELIMO headquarters. In the Jardim neighborhood, the Cervejas de Mocambique factory was invaded and looted. In the Luis Cabral neighborhood, residents set on fire the community school and destroyed all its facilities. They shot dead at least 1 man in the Magoanine C neighborhood (coded separately) and another one in Zimpeto. An unspecified number of people were injured by gunshots, including people who were not demonstrating. ---- Around 15 January 2025 (month of), PODEMOS supporters destroyed (means unspecified) the Herois Mocambicanos secondary school and the Sao Francisco Xavier community school during demonstrations in the KaMubukwana and the George Dimitrov neighborhoods of Maputo (Maputo City - Kamubukwana, Maputo City). In the Sao Francisco Xavier school, the library, the teachers' lounge, and the computer room were vandalized. These events happened in the context of nationwide demonstrations and unrest against election results. ---- On 20 January 2025, striking teachers and other employees of the Maputo International School, with signs in hand, gathered at its entrance in Maputo (Maputo City - Kampfumo, Maputo City), demanding their 3-month arrears of salaries and a change of management. They also protested against the inequality of treatment between local and foreign teachers. ---- On 6 February 2025, Mondlane (PODEMOS-affiliated) supporters protested near shops in Bagamoio and George Dimitrov neighborhoods in Maputo (Maputo City - Kamubukwana, Maputo, Maputo City) to demand a reduction in prices. They also visited Benfica Secondary School to ensure students were not paying school fees to attend. In one area, authorities (type unspecified) intervened. These are demands called for by Mondlane in post-election protests. ---- On 3 March 2025, teachers from the Portuguese School of Mozambique protested in Maputo (Maputo, Maputo City), demanding equal working conditions for professionals on mobility. They threatened to strike over salary disparities. ---- On 5 March 2025, hundreds of anti-government protesters and supporters of Mondlane marched in the Hulene neighborhood of Maputo City (Maputo, Maputo City) against his exclusion from the political agreement set to be signed by President Chapo with main political parties the same day. Heavily armed police officers launched tear gas, explosives and fired live ammunition at Mondlane who was haranguing his supporters from the sunroof of an SUV, resulting in at least 16 people injured by gunshots, including Mondlane's camera person. According to Mondlane's team, 2 children from a nearby school died from the shooting. Following the police gunshots, people blocked the highway using buses, tires and stones, and a private passenger bus was set on fire. ---- On 5 June 2025, dozens of students at Eduardo Mondlane University demonstrated on campus in Maputo (Maputo City - Kampfumo, Maputo, Maputo City) against the cancellation of their university registrations. The university claims their payments were late and they will only be able to attend classes again in the first semester of 2026.</t>
+        </is>
+      </c>
+      <c r="BJ34" t="inlineStr">
+        <is>
+          <t>2024-01-29 ---- 2024-02-05 ---- 2024-10-09 ---- 2024-10-21 ---- 2024-10-24 ---- 2024-10-24 ---- 2024-10-25 ---- 2024-10-31 ---- 2024-11-04 ---- 2024-11-04 ---- 2024-11-04 ---- 2024-11-05 ---- 2024-11-13 ---- 2024-11-15 ---- 2024-11-16 ---- 2024-11-18 ---- 2024-11-21 ---- 2024-11-21 ---- 2024-11-21 ---- 2024-11-21 ---- 2024-12-02 ---- 2024-12-23 ---- 2025-01-15 ---- 2025-01-20 ---- 2025-02-06 ---- 2025-03-03 ---- 2025-03-05 ---- 2025-06-05</t>
+        </is>
+      </c>
+      <c r="BK34" t="inlineStr">
+        <is>
+          <t>Maputo</t>
+        </is>
+      </c>
       <c r="BL34" t="n">
         <v>0</v>
       </c>
@@ -5125,7 +5099,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MZ0716</t>
+          <t>MZ0701</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -5134,7 +5108,7 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MZ0806</t>
+          <t>MZ0812</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5143,25 +5117,25 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>85.78</v>
+        <v>20</v>
       </c>
       <c r="I35" t="n">
-        <v>11.21</v>
+        <v>80</v>
       </c>
       <c r="J35" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>26.48</v>
+        <v>123.61</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5170,7 +5144,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -5179,13 +5153,13 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
@@ -5214,20 +5188,68 @@
       <c r="AU35" t="inlineStr"/>
       <c r="AV35" t="inlineStr"/>
       <c r="AW35" t="inlineStr"/>
-      <c r="AX35" t="inlineStr"/>
-      <c r="AY35" t="inlineStr"/>
-      <c r="AZ35" t="inlineStr"/>
-      <c r="BA35" t="inlineStr"/>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>MZ07</t>
+        </is>
+      </c>
       <c r="BB35" t="inlineStr"/>
-      <c r="BC35" t="inlineStr"/>
-      <c r="BD35" t="inlineStr"/>
-      <c r="BE35" t="inlineStr"/>
-      <c r="BF35" t="inlineStr"/>
-      <c r="BG35" t="inlineStr"/>
-      <c r="BH35" t="inlineStr"/>
-      <c r="BI35" t="inlineStr"/>
-      <c r="BJ35" t="inlineStr"/>
-      <c r="BK35" t="inlineStr"/>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>Strategic developments</t>
+        </is>
+      </c>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="BE35" t="inlineStr">
+        <is>
+          <t>FRELIMO: Liberation Front of Mozambique</t>
+        </is>
+      </c>
+      <c r="BF35" t="inlineStr">
+        <is>
+          <t>Government of Mozambique (1990-)</t>
+        </is>
+      </c>
+      <c r="BG35" t="inlineStr">
+        <is>
+          <t>Civilians (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>Journalists (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BI35" t="inlineStr">
+        <is>
+          <t>Other: On 24 August 2024, an assistant of the Agoche's mayor (FRELIMO member) beat a photojournalist (Paraphato radio) who was filming the start of Frelimo's election campaign at Farlahe Primary School in Inguri neighborhood in Angoche (Angoche, Nampula), and seized his camera. Extent of injuries unknown/not reported. The Community Radio Forum (FORCOM) claimed that the Angoche Mayor and the FRELIMO First Secretary in Angoche were responsible for the attack. Another radio journalist had his material seized on the following day (coded separately). The incident happened in the context of the upcoming October 2024 general election.</t>
+        </is>
+      </c>
+      <c r="BJ35" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="BK35" t="inlineStr">
+        <is>
+          <t>Angoche</t>
+        </is>
+      </c>
       <c r="BL35" t="n">
         <v>0</v>
       </c>
@@ -5235,7 +5257,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MZ0717</t>
+          <t>MZ0702</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -5244,7 +5266,7 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MZ0108</t>
+          <t>MZ0717</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5253,19 +5275,19 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>61.76</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>32.35</v>
+        <v>0.54</v>
       </c>
       <c r="J36" t="n">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>42.14</v>
+        <v>3.95</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -5280,7 +5302,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -5289,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>7.07</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -5330,10 +5352,10 @@
         </is>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -5343,47 +5365,47 @@
       <c r="BB36" t="inlineStr"/>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>Riots</t>
+          <t>Riots ---- Riots ---- Riots ---- Riots</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>Violent demonstration</t>
+          <t>Violent demonstration ---- Violent demonstration ---- Violent demonstration ---- Violent demonstration</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>Rioters (Mozambique)</t>
+          <t>Rioters (Mozambique) ---- Rioters (Mozambique) ---- Rioters (Mozambique) ---- Rioters (Mozambique)</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>PODEMOS: Optimistic Party for the Development of Mozambique</t>
+          <t>PODEMOS: Optimistic Party for the Development of Mozambique ---- PODEMOS: Optimistic Party for the Development of Mozambique ---- PODEMOS: Optimistic Party for the Development of Mozambique ---- Students (Mozambique)</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr">
         <is>
-          <t>Civilians (Mozambique)</t>
+          <t>Police Forces of Mozambique (1990-) ---- Police Forces of Mozambique (1990-) Rapid Intervention Unit ---- Civilians (Mozambique)</t>
         </is>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>FRELIMO: Liberation Front of Mozambique; Government of Mozambique (1990-); Private Security Forces (Mozambique); Students (Mozambique)</t>
+          <t>Private Security Forces (Mozambique) ---- Police Forces of Mozambique (1990-); Teachers (Mozambique)</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>On 4 December 2024, PODEMOS supporters gathered in Muecate (Muecate, Nampula), following a call by the PODEMOS presidential candidate for a 8-day demonstration against the election results. The crowd invaded the FRELIMO district committee premises and scattered on the street hundreds of voter cards. They forced students at the local secondary school to abandon their exams. They set on fire the headquarters of the Mozambican Women's Organization, the houses of the first secretary of Frelimo, the party security guard and the district director of the Technical Secretariat for Electoral Administration.</t>
+          <t>Around 7 December 2024 (as reported), PODEMOS supporters attempted to invade the residence of the governor in Nampula (Nampula, Nampula) during a demonstration against election results. Police officers shot a former municipal councilor for education while he was at Cafe Atlantico. Severely injured, he was hospitalized and died on 7 December. ---- Around 15 December 2024 (month of), PODEMOS supporters looted 27 computers and 24 tablets from Namicopo secondary school in Nampula (Nampula, Nampula). They destroyed the computer room, the doors of several compartments and classrooms, and burned documents. The event happened in the context of nationwide demonstrations and unrest against election results. ---- On 24 December 2024, for the second consecutive day, hundreds of PODEMOS supporters blocked (means unspecified) the main roads in several neighborhoods of Nampula (Nampula, Nampula), following a call by the PODEMOS presidential candidate after the announcement on 23 December by the constitutional council of the victory of the FRELIMO party in the presidential, legislative, and provincial elections on 23 December. Commercial establishments were vandalized and looted in the main neighborhoods of Nampula: in the Nasser area, in Muahivire, in Namicopo, and the Mutava Rex area. Several public and private infrastructures were destroyed in Namicopo: hospitals, administrative buildings, police stations, schools, and shopping centers. In Namiepe, rioters destroyed a police station and looted a chicken company. The house of the archdiocese was also looted and hundreds of prisoners at the Northern regional penitentiary establishment attempted to escape. There were clashes (means unspecified) between demonstrators and police officers supported by private security agents. 22 people were killed in the city from 23 December to 26 December (17 arrived dead at the hospital and 4 died upon arrival), and at least 116 were injured and hospitalized, 38 of them with serious conditions. 22 fatalities split across three days and coded as 7 for this event. ---- On 6 March 2025, rioters, suspected supporters of Mondlane (former presidential candidate), barricaded roads with burning tires in Nampula (Nampula, Nampula) during a demonstration against the general election results held in October 2024. At the Waresta Market, Serra da Mesa, Controle, and Angoche Station, rioters threatened local shopkeepers and burned down a vehicle. Students attacked (means unspecified) the school principal and an unspecified number of employees of the Motomoti Elementary School. They also destroyed its administrative block. The school principal had to be hospitalized. Police officers arrested 10 people.</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024-12-07 ---- 2024-12-15 ---- 2024-12-24 ---- 2025-03-06</t>
         </is>
       </c>
       <c r="BK36" t="inlineStr">
         <is>
-          <t>Muecate</t>
+          <t>Nampula</t>
         </is>
       </c>
       <c r="BL36" t="n">
@@ -5393,7 +5415,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MZ0718</t>
+          <t>MZ0703</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -5402,31 +5424,31 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>MZ0723</t>
+          <t>MZ0801</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
+          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>100</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>14.08</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>21.76</v>
+        <v>51.96</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -5438,7 +5460,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -5447,10 +5469,10 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>9.629999999999999</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -5482,20 +5504,60 @@
       <c r="AU37" t="inlineStr"/>
       <c r="AV37" t="inlineStr"/>
       <c r="AW37" t="inlineStr"/>
-      <c r="AX37" t="inlineStr"/>
-      <c r="AY37" t="inlineStr"/>
-      <c r="AZ37" t="inlineStr"/>
-      <c r="BA37" t="inlineStr"/>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="AY37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>MZ07</t>
+        </is>
+      </c>
       <c r="BB37" t="inlineStr"/>
-      <c r="BC37" t="inlineStr"/>
-      <c r="BD37" t="inlineStr"/>
-      <c r="BE37" t="inlineStr"/>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>Violence against civilians ---- Violence against civilians ---- Violence against civilians</t>
+        </is>
+      </c>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>Attack ---- Attack ---- Attack</t>
+        </is>
+      </c>
+      <c r="BE37" t="inlineStr">
+        <is>
+          <t>Islamic State Mozambique (ISM) ---- Islamic State Mozambique (ISM) ---- Islamic State Mozambique (ISM)</t>
+        </is>
+      </c>
       <c r="BF37" t="inlineStr"/>
-      <c r="BG37" t="inlineStr"/>
+      <c r="BG37" t="inlineStr">
+        <is>
+          <t>Civilians (Mozambique) ---- Civilians (Mozambique) ---- Civilians (Mozambique)</t>
+        </is>
+      </c>
       <c r="BH37" t="inlineStr"/>
-      <c r="BI37" t="inlineStr"/>
-      <c r="BJ37" t="inlineStr"/>
-      <c r="BK37" t="inlineStr"/>
+      <c r="BI37" t="inlineStr">
+        <is>
+          <t>On 25 April 2024, Islamist militia attacked Nassua in the district of Erati (location coded to Erati, Erati, Nampula). The Islamic State claimed the attack and the killing of one person, the burning of a church, two 'Christian' schools, three motorcycles, and about 190 houses. ---- On 25 April 2024, Islamist militia attacked Odinepa (Memba, Nampula). Casualties unknown. Products were looted and houses and schools burned. ---- On 26 April 2024, Islamist militia attacked Manika in the district of Erati (location coded to Erati, Erati, Nampula). Casualties unknown. The Islamic State claimed the attack on a 'Christian' village and the burning of a church, a school and more than 30 houses.</t>
+        </is>
+      </c>
+      <c r="BJ37" t="inlineStr">
+        <is>
+          <t>2024-04-25 ---- 2024-04-25 ---- 2024-04-26</t>
+        </is>
+      </c>
+      <c r="BK37" t="inlineStr">
+        <is>
+          <t>Erati</t>
+        </is>
+      </c>
       <c r="BL37" t="n">
         <v>0</v>
       </c>
@@ -5503,7 +5565,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MZ0719</t>
+          <t>MZ0704</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -5512,43 +5574,43 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MZ0410</t>
+          <t>MZ1114</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
+          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>65.88</v>
+        <v>68.97</v>
       </c>
       <c r="I38" t="n">
-        <v>32.23</v>
+        <v>31.03</v>
       </c>
       <c r="J38" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>57.52</v>
+        <v>60.32</v>
       </c>
       <c r="M38" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -5557,13 +5619,13 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
@@ -5613,68 +5675,30 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MZ0720</t>
+          <t>MZ0705</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>MZ0410</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>76.83</v>
-      </c>
-      <c r="I39" t="n">
-        <v>23.17</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>42.06</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
@@ -5702,20 +5726,64 @@
       <c r="AU39" t="inlineStr"/>
       <c r="AV39" t="inlineStr"/>
       <c r="AW39" t="inlineStr"/>
-      <c r="AX39" t="inlineStr"/>
-      <c r="AY39" t="inlineStr"/>
-      <c r="AZ39" t="inlineStr"/>
-      <c r="BA39" t="inlineStr"/>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>MZ07</t>
+        </is>
+      </c>
       <c r="BB39" t="inlineStr"/>
-      <c r="BC39" t="inlineStr"/>
-      <c r="BD39" t="inlineStr"/>
-      <c r="BE39" t="inlineStr"/>
-      <c r="BF39" t="inlineStr"/>
-      <c r="BG39" t="inlineStr"/>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>Riots</t>
+        </is>
+      </c>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>Violent demonstration</t>
+        </is>
+      </c>
+      <c r="BE39" t="inlineStr">
+        <is>
+          <t>Rioters (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BF39" t="inlineStr">
+        <is>
+          <t>PODEMOS: Optimistic Party for the Development of Mozambique</t>
+        </is>
+      </c>
+      <c r="BG39" t="inlineStr">
+        <is>
+          <t>Police Forces of Mozambique (1990-)</t>
+        </is>
+      </c>
       <c r="BH39" t="inlineStr"/>
-      <c r="BI39" t="inlineStr"/>
-      <c r="BJ39" t="inlineStr"/>
-      <c r="BK39" t="inlineStr"/>
+      <c r="BI39" t="inlineStr">
+        <is>
+          <t>On 7 November 2024, PODEMOS supporters attempted to vandalize the Secondary School of Lalaua in Lalaua (Lalaua, Nampula), following a call by the PODEMOS presidential candidate for a seven-day national strike. The demonstration was held against police violence during previous PODEMOS-led demonstrations, claims of the assassination of the PODEMOS presidential candidate's legal adviser and legal representative by special forces (coded separately), and what they consider fraudulent general election results. Police officers intervened firing tear gas and arresting 3 people. Injuries unknown/not reported. The incident happened after the announcement of the final results of the 2024 general election.</t>
+        </is>
+      </c>
+      <c r="BJ39" t="inlineStr">
+        <is>
+          <t>2024-11-07</t>
+        </is>
+      </c>
+      <c r="BK39" t="inlineStr">
+        <is>
+          <t>Lalaua</t>
+        </is>
+      </c>
       <c r="BL39" t="n">
         <v>0</v>
       </c>
@@ -5723,68 +5791,30 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MZ0721</t>
+          <t>MZ0706</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>MZ0101</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>94.87</v>
-      </c>
-      <c r="I40" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="J40" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
@@ -5812,20 +5842,56 @@
       <c r="AU40" t="inlineStr"/>
       <c r="AV40" t="inlineStr"/>
       <c r="AW40" t="inlineStr"/>
-      <c r="AX40" t="inlineStr"/>
-      <c r="AY40" t="inlineStr"/>
-      <c r="AZ40" t="inlineStr"/>
-      <c r="BA40" t="inlineStr"/>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>MZ07</t>
+        </is>
+      </c>
       <c r="BB40" t="inlineStr"/>
-      <c r="BC40" t="inlineStr"/>
-      <c r="BD40" t="inlineStr"/>
-      <c r="BE40" t="inlineStr"/>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>Riots</t>
+        </is>
+      </c>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>Mob violence</t>
+        </is>
+      </c>
+      <c r="BE40" t="inlineStr">
+        <is>
+          <t>Rioters (Mozambique)</t>
+        </is>
+      </c>
       <c r="BF40" t="inlineStr"/>
       <c r="BG40" t="inlineStr"/>
       <c r="BH40" t="inlineStr"/>
-      <c r="BI40" t="inlineStr"/>
-      <c r="BJ40" t="inlineStr"/>
-      <c r="BK40" t="inlineStr"/>
+      <c r="BI40" t="inlineStr">
+        <is>
+          <t>On 20 March 2025, a mob vandalized a primary school by burning books and attacked the educational director's home in Topito (Larde, Larde, Nampula), accusing the director of spreading cholera amongst communities. Residents claimed the mob came from outside the district.</t>
+        </is>
+      </c>
+      <c r="BJ40" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="BK40" t="inlineStr">
+        <is>
+          <t>Larde</t>
+        </is>
+      </c>
       <c r="BL40" t="n">
         <v>0</v>
       </c>
@@ -5833,7 +5899,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MZ0722</t>
+          <t>MZ0707</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -5851,10 +5917,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>91.3</v>
+        <v>85</v>
       </c>
       <c r="I41" t="n">
-        <v>8.699999999999999</v>
+        <v>15</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5863,7 +5929,7 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>33.57</v>
+        <v>44.86</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -5893,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
@@ -5943,7 +6009,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MZ0723</t>
+          <t>MZ0708</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -5961,10 +6027,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>84.62</v>
+        <v>95.56</v>
       </c>
       <c r="I42" t="n">
-        <v>15.38</v>
+        <v>4.44</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5973,7 +6039,7 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>35.28</v>
+        <v>22.96</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -6053,7 +6119,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MZ0801</t>
+          <t>MZ0709</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -6062,19 +6128,19 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MZ0812</t>
+          <t>MZ1122</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
+          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>88.89</v>
+        <v>87.72</v>
       </c>
       <c r="I43" t="n">
-        <v>11.11</v>
+        <v>12.28</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -6083,7 +6149,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>77.48999999999999</v>
+        <v>20.1</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -6104,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
@@ -6163,7 +6229,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MZ0802</t>
+          <t>MZ0710</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -6172,7 +6238,7 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MZ1114</t>
+          <t>MZ0722</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6181,10 +6247,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>83.15000000000001</v>
+        <v>78.41</v>
       </c>
       <c r="I44" t="n">
-        <v>16.85</v>
+        <v>21.59</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -6193,7 +6259,7 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>34.63</v>
+        <v>47.65</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -6208,7 +6274,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -6223,7 +6289,7 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
@@ -6273,7 +6339,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MZ0803</t>
+          <t>MZ0711</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -6282,28 +6348,28 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MZ0102</t>
+          <t>MZ0107</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
+          <t>MZ0107;MZ0110;MZ0403;MZ0711</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>82.04000000000001</v>
+        <v>72.41</v>
       </c>
       <c r="I45" t="n">
-        <v>16.77</v>
+        <v>25.29</v>
       </c>
       <c r="J45" t="n">
-        <v>0.6</v>
+        <v>1.15</v>
       </c>
       <c r="K45" t="n">
-        <v>0.6</v>
+        <v>1.15</v>
       </c>
       <c r="L45" t="n">
-        <v>29.9</v>
+        <v>56.47</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -6312,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.14</v>
+        <v>0.48</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -6330,10 +6396,10 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="V45" t="n">
-        <v>0.6</v>
+        <v>1.63</v>
       </c>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
@@ -6383,7 +6449,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MZ0806</t>
+          <t>MZ0712</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -6392,7 +6458,7 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MZ0701</t>
+          <t>MZ0813</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6401,19 +6467,19 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>71.43000000000001</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>23.81</v>
+        <v>33.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>70.15000000000001</v>
+        <v>84.08</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6437,13 +6503,13 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>5.109999999999999</v>
+        <v>0.35</v>
       </c>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
@@ -6493,7 +6559,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MZ0808</t>
+          <t>MZ0713</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -6502,28 +6568,28 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MZ0817</t>
+          <t>MZ1106</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
+          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>93.75</v>
+        <v>100</v>
       </c>
       <c r="I47" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>63.69</v>
+        <v>16.49</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -6535,10 +6601,10 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -6603,68 +6669,30 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MZ0809</t>
+          <t>MZ0714</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>MZ0712</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="I48" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>86.19999999999999</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
@@ -6692,20 +6720,64 @@
       <c r="AU48" t="inlineStr"/>
       <c r="AV48" t="inlineStr"/>
       <c r="AW48" t="inlineStr"/>
-      <c r="AX48" t="inlineStr"/>
-      <c r="AY48" t="inlineStr"/>
-      <c r="AZ48" t="inlineStr"/>
-      <c r="BA48" t="inlineStr"/>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="AY48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA48" t="inlineStr">
+        <is>
+          <t>MZ07</t>
+        </is>
+      </c>
       <c r="BB48" t="inlineStr"/>
-      <c r="BC48" t="inlineStr"/>
-      <c r="BD48" t="inlineStr"/>
-      <c r="BE48" t="inlineStr"/>
-      <c r="BF48" t="inlineStr"/>
-      <c r="BG48" t="inlineStr"/>
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>Protests ---- Riots</t>
+        </is>
+      </c>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>Excessive force against protesters ---- Mob violence</t>
+        </is>
+      </c>
+      <c r="BE48" t="inlineStr">
+        <is>
+          <t>Protesters (Mozambique) ---- Rioters (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BF48" t="inlineStr">
+        <is>
+          <t>Civilians (Mozambique); PODEMOS: Optimistic Party for the Development of Mozambique; Students (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BG48" t="inlineStr">
+        <is>
+          <t>Police Forces of Mozambique (1990-)</t>
+        </is>
+      </c>
       <c r="BH48" t="inlineStr"/>
-      <c r="BI48" t="inlineStr"/>
-      <c r="BJ48" t="inlineStr"/>
-      <c r="BK48" t="inlineStr"/>
+      <c r="BI48" t="inlineStr">
+        <is>
+          <t>On 21 November 2024, PODEMOS supporters protested in Moma (Moma, Nampula), following a call by the PODEMOS presidential candidate for a three-day national strike. The demonstration was held as part of phase four of PODEMOS-led demonstrations, against police violence during previous PODEMOS-led demonstrations, to mourn the deaths of about 50 people who were shot by police officers. Police officers intervened firing live bullets. A school pupil was shot on a bridge on his way home from school and died. Five people were injured. Extent of injuries unknown/not reported. ---- On 21 March 2025, a mob vandalized a school in the Pilivili neighborhood (Moma, Chalaua, Moma, Nampula). The attack was likely due to a similar mob accusation and attack over the spread of cholera due in Topito (coded separately).</t>
+        </is>
+      </c>
+      <c r="BJ48" t="inlineStr">
+        <is>
+          <t>2024-11-21 ---- 2025-03-21</t>
+        </is>
+      </c>
+      <c r="BK48" t="inlineStr">
+        <is>
+          <t>Moma</t>
+        </is>
+      </c>
       <c r="BL48" t="n">
         <v>0</v>
       </c>
@@ -6713,7 +6785,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MZ0810</t>
+          <t>MZ0715</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -6722,31 +6794,31 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MZ1006</t>
+          <t>MZ0913</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
+          <t>MZ0715;MZ0907;MZ0913</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>84.78</v>
+        <v>81.31</v>
       </c>
       <c r="I49" t="n">
-        <v>10.87</v>
+        <v>18.69</v>
       </c>
       <c r="J49" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>28.28</v>
+        <v>28.33</v>
       </c>
       <c r="M49" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -6758,7 +6830,7 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -6767,13 +6839,13 @@
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="V49" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
@@ -6823,7 +6895,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MZ0811</t>
+          <t>MZ0716</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -6832,31 +6904,31 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MZ1101</t>
+          <t>MZ0806</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
+          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>100</v>
+        <v>85.78</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>11.21</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>20.09</v>
+        <v>26.48</v>
       </c>
       <c r="M50" t="n">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -6868,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.57</v>
+        <v>0.37</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
@@ -6877,13 +6949,13 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U50" t="n">
-        <v>0.45</v>
+        <v>1.85</v>
       </c>
       <c r="V50" t="n">
-        <v>0.45</v>
+        <v>0.19</v>
       </c>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
@@ -6933,7 +7005,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MZ0813</t>
+          <t>MZ0717</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -6942,28 +7014,28 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MZ1111</t>
+          <t>MZ0108</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
+          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>100</v>
+        <v>61.76</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>32.35</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>34.21</v>
+        <v>42.14</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -6978,22 +7050,22 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>7.07</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
@@ -7022,20 +7094,68 @@
       <c r="AU51" t="inlineStr"/>
       <c r="AV51" t="inlineStr"/>
       <c r="AW51" t="inlineStr"/>
-      <c r="AX51" t="inlineStr"/>
-      <c r="AY51" t="inlineStr"/>
-      <c r="AZ51" t="inlineStr"/>
-      <c r="BA51" t="inlineStr"/>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Nampula</t>
+        </is>
+      </c>
+      <c r="AY51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>MZ07</t>
+        </is>
+      </c>
       <c r="BB51" t="inlineStr"/>
-      <c r="BC51" t="inlineStr"/>
-      <c r="BD51" t="inlineStr"/>
-      <c r="BE51" t="inlineStr"/>
-      <c r="BF51" t="inlineStr"/>
-      <c r="BG51" t="inlineStr"/>
-      <c r="BH51" t="inlineStr"/>
-      <c r="BI51" t="inlineStr"/>
-      <c r="BJ51" t="inlineStr"/>
-      <c r="BK51" t="inlineStr"/>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>Riots</t>
+        </is>
+      </c>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>Violent demonstration</t>
+        </is>
+      </c>
+      <c r="BE51" t="inlineStr">
+        <is>
+          <t>Rioters (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BF51" t="inlineStr">
+        <is>
+          <t>PODEMOS: Optimistic Party for the Development of Mozambique</t>
+        </is>
+      </c>
+      <c r="BG51" t="inlineStr">
+        <is>
+          <t>Civilians (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BH51" t="inlineStr">
+        <is>
+          <t>FRELIMO: Liberation Front of Mozambique; Government of Mozambique (1990-); Private Security Forces (Mozambique); Students (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BI51" t="inlineStr">
+        <is>
+          <t>On 4 December 2024, PODEMOS supporters gathered in Muecate (Muecate, Nampula), following a call by the PODEMOS presidential candidate for a 8-day demonstration against the election results. The crowd invaded the FRELIMO district committee premises and scattered on the street hundreds of voter cards. They forced students at the local secondary school to abandon their exams. They set on fire the headquarters of the Mozambican Women's Organization, the houses of the first secretary of Frelimo, the party security guard and the district director of the Technical Secretariat for Electoral Administration.</t>
+        </is>
+      </c>
+      <c r="BJ51" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="BK51" t="inlineStr">
+        <is>
+          <t>Muecate</t>
+        </is>
+      </c>
       <c r="BL51" t="n">
         <v>0</v>
       </c>
@@ -7043,7 +7163,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MZ0815</t>
+          <t>MZ0718</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -7052,7 +7172,7 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MZ0911</t>
+          <t>MZ0723</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7061,10 +7181,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>71.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="I52" t="n">
-        <v>28.57</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -7073,13 +7193,13 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>25.61</v>
+        <v>21.76</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7088,7 +7208,7 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -7100,10 +7220,10 @@
         <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
@@ -7153,7 +7273,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MZ0817</t>
+          <t>MZ0719</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -7162,43 +7282,43 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MZ0808</t>
+          <t>MZ0410</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
+          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>65.88</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>32.23</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="L53" t="n">
-        <v>56.08</v>
+        <v>57.52</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -7207,13 +7327,13 @@
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>0.68</v>
+        <v>0.47</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
@@ -7263,7 +7383,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MZ0818</t>
+          <t>MZ0720</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -7272,28 +7392,28 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>MZ1120</t>
+          <t>MZ0410</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>MZ0818;MZ1120</t>
+          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>60.78</v>
+        <v>76.83</v>
       </c>
       <c r="I54" t="n">
-        <v>35.29</v>
+        <v>23.17</v>
       </c>
       <c r="J54" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>52.73</v>
+        <v>42.06</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -7305,16 +7425,16 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
         <v>0</v>
@@ -7323,7 +7443,7 @@
         <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
@@ -7373,7 +7493,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MZ0819</t>
+          <t>MZ0721</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -7382,31 +7502,31 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MZ0801</t>
+          <t>MZ0101</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
+          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>60.47</v>
+        <v>94.87</v>
       </c>
       <c r="I55" t="n">
-        <v>37.21</v>
+        <v>2.56</v>
       </c>
       <c r="J55" t="n">
-        <v>2.33</v>
+        <v>2.56</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>75.55</v>
+        <v>3.91</v>
       </c>
       <c r="M55" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
@@ -7418,16 +7538,16 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>0.18</v>
+        <v>1.28</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -7483,7 +7603,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MZ0901</t>
+          <t>MZ0722</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -7492,31 +7612,31 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>MZ1013</t>
+          <t>MZ0710</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
+          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>84.70999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="I56" t="n">
-        <v>14.12</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>20.27</v>
+        <v>33.57</v>
       </c>
       <c r="M56" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
@@ -7528,7 +7648,7 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -7537,7 +7657,7 @@
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -7593,7 +7713,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MZ0902</t>
+          <t>MZ0723</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -7602,7 +7722,7 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>MZ0911</t>
+          <t>MZ0718</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -7611,22 +7731,22 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>66.13</v>
+        <v>84.62</v>
       </c>
       <c r="I57" t="n">
-        <v>25.88</v>
+        <v>15.38</v>
       </c>
       <c r="J57" t="n">
-        <v>7.99</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>43.06</v>
+        <v>35.28</v>
       </c>
       <c r="M57" t="n">
-        <v>8.67</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
@@ -7638,7 +7758,7 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -7703,7 +7823,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MZ0905</t>
+          <t>MZ0801</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -7712,28 +7832,28 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>MZ0811</t>
+          <t>MZ0812</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
+          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>83.97</v>
+        <v>88.89</v>
       </c>
       <c r="I58" t="n">
-        <v>15.61</v>
+        <v>11.11</v>
       </c>
       <c r="J58" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>29.05</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -7748,22 +7868,22 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
@@ -7813,7 +7933,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MZ0907</t>
+          <t>MZ0802</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -7822,19 +7942,19 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>MZ0715</t>
+          <t>MZ1114</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>MZ0715;MZ0907;MZ0913</t>
+          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>84.84999999999999</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>15.15</v>
+        <v>16.85</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -7843,7 +7963,7 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>20.38</v>
+        <v>34.63</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -7855,10 +7975,10 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.7</v>
+        <v>0.48</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -7867,13 +7987,13 @@
         <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="U59" t="n">
         <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
@@ -7923,7 +8043,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MZ0911</t>
+          <t>MZ0803</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -7932,28 +8052,28 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MZ0902</t>
+          <t>MZ0102</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
+          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>76.19</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>22.86</v>
+        <v>16.77</v>
       </c>
       <c r="J60" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L60" t="n">
-        <v>38.5</v>
+        <v>29.9</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -7968,7 +8088,7 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -7977,13 +8097,13 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr"/>
@@ -8033,7 +8153,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MZ0913</t>
+          <t>MZ0806</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -8042,34 +8162,34 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>MZ0715</t>
+          <t>MZ0701</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>MZ0715;MZ0907;MZ0913</t>
+          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>86.17</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>11.07</v>
+        <v>23.81</v>
       </c>
       <c r="J61" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="L61" t="n">
-        <v>23.63</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8078,22 +8198,22 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>1.19</v>
+        <v>0.7</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>5.109999999999999</v>
       </c>
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
@@ -8143,7 +8263,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MZ1006</t>
+          <t>MZ0808</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -8152,31 +8272,31 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MZ0810</t>
+          <t>MZ0817</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
+          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>84.92</v>
+        <v>93.75</v>
       </c>
       <c r="I62" t="n">
-        <v>10.05</v>
+        <v>3.12</v>
       </c>
       <c r="J62" t="n">
-        <v>2.51</v>
+        <v>3.12</v>
       </c>
       <c r="K62" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>21.05</v>
+        <v>63.69</v>
       </c>
       <c r="M62" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
@@ -8185,10 +8305,10 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.01</v>
+        <v>3.69</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -8197,13 +8317,13 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>5.51</v>
+        <v>0</v>
       </c>
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
@@ -8232,64 +8352,20 @@
       <c r="AU62" t="inlineStr"/>
       <c r="AV62" t="inlineStr"/>
       <c r="AW62" t="inlineStr"/>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>Tete</t>
-        </is>
-      </c>
-      <c r="AY62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ62" t="n">
-        <v>3</v>
-      </c>
-      <c r="BA62" t="inlineStr">
-        <is>
-          <t>MZ10</t>
-        </is>
-      </c>
+      <c r="AX62" t="inlineStr"/>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr"/>
+      <c r="BA62" t="inlineStr"/>
       <c r="BB62" t="inlineStr"/>
-      <c r="BC62" t="inlineStr">
-        <is>
-          <t>Protests ---- Protests ---- Riots</t>
-        </is>
-      </c>
-      <c r="BD62" t="inlineStr">
-        <is>
-          <t>Peaceful protest ---- Excessive force against protesters ---- Violent demonstration</t>
-        </is>
-      </c>
-      <c r="BE62" t="inlineStr">
-        <is>
-          <t>Protesters (Mozambique) ---- Protesters (Mozambique) ---- Rioters (Mozambique)</t>
-        </is>
-      </c>
-      <c r="BF62" t="inlineStr">
-        <is>
-          <t>Students (Mozambique) ---- PODEMOS: Optimistic Party for the Development of Mozambique ---- PODEMOS: Optimistic Party for the Development of Mozambique</t>
-        </is>
-      </c>
-      <c r="BG62" t="inlineStr">
-        <is>
-          <t>Police Forces of Mozambique (1990-)</t>
-        </is>
-      </c>
+      <c r="BC62" t="inlineStr"/>
+      <c r="BD62" t="inlineStr"/>
+      <c r="BE62" t="inlineStr"/>
+      <c r="BF62" t="inlineStr"/>
+      <c r="BG62" t="inlineStr"/>
       <c r="BH62" t="inlineStr"/>
-      <c r="BI62" t="inlineStr">
-        <is>
-          <t>On 14 September 2024, more than 100 medical students who attended the Faculty of Health Sciences at the University of Zambeze marched in Tete (Tete, Tete) against alleged lack of contracts for integrated internships. Students marched from the installations of Unizambeze to Independence Square. Students complained about lack of communication and alleged imposition of contracts to access the integrated internships, accusing the institution's management of acting outside the law. ---- On 4 November 2024, PODEMOS supporters demonstrated in Tete (Tete, Tete), following a call by the PODEMOS presidential candidate for a seven-day national strike and protests. The demonstration was held to protest police violence during previous PODEMOS-led demonstrations, claims of the assassination of the PODEMOS presidential candidate's legal adviser and legal representative by special forces (coded separately), and what they consider fraudulent general election results. Police officers intervened firing tear gas at the ground of Castro Teofilo school. Center for Public Integrity (CJP) claimed one person was killed. The incident happened after the announcement of the final results of the 2024 general election. ---- Around 25 January 2025 (as reported), PODEMOS supporters destroyed at least 5 schools, including the Cateme secondary school, the Benga basic school, and the Oitavadas basic school during a demonstration in Tete province (Tete, Tete). In the Cateme secondary school, the library, the computer room, and the administrative block were vandalized. The event happened in the context of nationwide demonstrations and unrest against election results.</t>
-        </is>
-      </c>
-      <c r="BJ62" t="inlineStr">
-        <is>
-          <t>2024-09-14 ---- 2024-11-04 ---- 2025-01-25</t>
-        </is>
-      </c>
-      <c r="BK62" t="inlineStr">
-        <is>
-          <t>Tete</t>
-        </is>
-      </c>
+      <c r="BI62" t="inlineStr"/>
+      <c r="BJ62" t="inlineStr"/>
+      <c r="BK62" t="inlineStr"/>
       <c r="BL62" t="n">
         <v>0</v>
       </c>
@@ -8297,7 +8373,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MZ1013</t>
+          <t>MZ0809</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -8306,31 +8382,31 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MZ1113</t>
+          <t>MZ0712</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
+          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>78.34</v>
+        <v>66.67</v>
       </c>
       <c r="I63" t="n">
-        <v>19.82</v>
+        <v>33.33</v>
       </c>
       <c r="J63" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>44.17</v>
+        <v>86.19999999999999</v>
       </c>
       <c r="M63" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
@@ -8342,7 +8418,7 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -8351,13 +8427,13 @@
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr"/>
@@ -8407,7 +8483,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MZ1101</t>
+          <t>MZ0810</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -8416,7 +8492,7 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>MZ0708</t>
+          <t>MZ1006</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -8425,25 +8501,25 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>93.33</v>
+        <v>84.78</v>
       </c>
       <c r="I64" t="n">
-        <v>6.67</v>
+        <v>10.87</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>20.13</v>
+        <v>28.28</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="N64" t="n">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8452,7 +8528,7 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.54</v>
+        <v>2.17</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -8467,7 +8543,7 @@
         <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr"/>
@@ -8517,7 +8593,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MZ1106</t>
+          <t>MZ0811</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -8526,7 +8602,7 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MZ0713</t>
+          <t>MZ1101</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -8535,10 +8611,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I65" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -8547,10 +8623,10 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>31.27</v>
+        <v>20.09</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
@@ -8562,7 +8638,7 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.41</v>
+        <v>3.57</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
@@ -8574,10 +8650,10 @@
         <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr"/>
@@ -8627,7 +8703,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MZ1111</t>
+          <t>MZ0813</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -8636,7 +8712,7 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MZ0813</t>
+          <t>MZ1111</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -8645,19 +8721,19 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>86.17</v>
+        <v>100</v>
       </c>
       <c r="I66" t="n">
-        <v>12.77</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>30.22</v>
+        <v>34.21</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -8666,28 +8742,28 @@
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="T66" t="n">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr"/>
@@ -8737,7 +8813,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MZ1113</t>
+          <t>MZ0815</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -8746,7 +8822,7 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MZ1013</t>
+          <t>MZ0911</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -8755,10 +8831,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>96.88</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>3.12</v>
+        <v>28.57</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -8767,13 +8843,13 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>14.66</v>
+        <v>25.61</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8782,7 +8858,7 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.89</v>
+        <v>5.03</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
@@ -8791,13 +8867,13 @@
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="inlineStr"/>
@@ -8847,7 +8923,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MZ1114</t>
+          <t>MZ0817</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -8856,7 +8932,7 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MZ0802</t>
+          <t>MZ0808</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -8865,19 +8941,19 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>90.31999999999999</v>
+        <v>100</v>
       </c>
       <c r="I68" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>25.05</v>
+        <v>56.08</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -8892,7 +8968,7 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
@@ -8901,10 +8977,10 @@
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="U68" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="V68" t="n">
         <v>0</v>
@@ -8936,68 +9012,20 @@
       <c r="AU68" t="inlineStr"/>
       <c r="AV68" t="inlineStr"/>
       <c r="AW68" t="inlineStr"/>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Zambezia</t>
-        </is>
-      </c>
-      <c r="AY68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ68" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA68" t="inlineStr">
-        <is>
-          <t>MZ11</t>
-        </is>
-      </c>
+      <c r="AX68" t="inlineStr"/>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr"/>
+      <c r="BA68" t="inlineStr"/>
       <c r="BB68" t="inlineStr"/>
-      <c r="BC68" t="inlineStr">
-        <is>
-          <t>Riots</t>
-        </is>
-      </c>
-      <c r="BD68" t="inlineStr">
-        <is>
-          <t>Mob violence</t>
-        </is>
-      </c>
-      <c r="BE68" t="inlineStr">
-        <is>
-          <t>Rioters (Mozambique)</t>
-        </is>
-      </c>
-      <c r="BF68" t="inlineStr">
-        <is>
-          <t>Vigilante Group (Mozambique)</t>
-        </is>
-      </c>
-      <c r="BG68" t="inlineStr">
-        <is>
-          <t>Civilians (Mozambique)</t>
-        </is>
-      </c>
-      <c r="BH68" t="inlineStr">
-        <is>
-          <t>Teachers (Mozambique)</t>
-        </is>
-      </c>
-      <c r="BI68" t="inlineStr">
-        <is>
-          <t>Around 19 July 2025 (as reported), residents beat 4 teachers in Cubeliua neighborhood of Mocuba (Mocuba, Zambezia), accusing them of trafficking albinos and their organs. No deaths reported.</t>
-        </is>
-      </c>
-      <c r="BJ68" t="inlineStr">
-        <is>
-          <t>2025-07-19</t>
-        </is>
-      </c>
-      <c r="BK68" t="inlineStr">
-        <is>
-          <t>Mocuba</t>
-        </is>
-      </c>
+      <c r="BC68" t="inlineStr"/>
+      <c r="BD68" t="inlineStr"/>
+      <c r="BE68" t="inlineStr"/>
+      <c r="BF68" t="inlineStr"/>
+      <c r="BG68" t="inlineStr"/>
+      <c r="BH68" t="inlineStr"/>
+      <c r="BI68" t="inlineStr"/>
+      <c r="BJ68" t="inlineStr"/>
+      <c r="BK68" t="inlineStr"/>
       <c r="BL68" t="n">
         <v>0</v>
       </c>
@@ -9005,7 +9033,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MZ1120</t>
+          <t>MZ0818</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -9014,7 +9042,7 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MZ0818</t>
+          <t>MZ1120</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -9023,19 +9051,19 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>89.38</v>
+        <v>60.78</v>
       </c>
       <c r="I69" t="n">
-        <v>8.85</v>
+        <v>35.29</v>
       </c>
       <c r="J69" t="n">
-        <v>1.33</v>
+        <v>1.96</v>
       </c>
       <c r="K69" t="n">
-        <v>0.44</v>
+        <v>1.96</v>
       </c>
       <c r="L69" t="n">
-        <v>19.34</v>
+        <v>52.73</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -9047,25 +9075,25 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.25</v>
+        <v>7.56</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="T69" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>0.44</v>
+        <v>2.62</v>
       </c>
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr"/>
@@ -9115,7 +9143,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MZ1122</t>
+          <t>MZ0819</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -9124,34 +9152,34 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MZ0709</t>
+          <t>MZ0801</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
+          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>83.33</v>
+        <v>60.47</v>
       </c>
       <c r="I70" t="n">
-        <v>12.18</v>
+        <v>37.21</v>
       </c>
       <c r="J70" t="n">
-        <v>4.49</v>
+        <v>2.33</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>20.69</v>
+        <v>75.55</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="N70" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9160,16 +9188,16 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T70" t="n">
-        <v>1.92</v>
+        <v>0.18</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
@@ -9219,6 +9247,2092 @@
       <c r="BJ70" t="inlineStr"/>
       <c r="BK70" t="inlineStr"/>
       <c r="BL70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>MZ0901</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>MZ1013</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>84.70999999999999</v>
+      </c>
+      <c r="I71" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="inlineStr"/>
+      <c r="AD71" t="inlineStr"/>
+      <c r="AE71" t="inlineStr"/>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr"/>
+      <c r="AJ71" t="inlineStr"/>
+      <c r="AK71" t="inlineStr"/>
+      <c r="AL71" t="inlineStr"/>
+      <c r="AM71" t="inlineStr"/>
+      <c r="AN71" t="inlineStr"/>
+      <c r="AO71" t="inlineStr"/>
+      <c r="AP71" t="inlineStr"/>
+      <c r="AQ71" t="inlineStr"/>
+      <c r="AR71" t="inlineStr"/>
+      <c r="AS71" t="inlineStr"/>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AU71" t="inlineStr"/>
+      <c r="AV71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr"/>
+      <c r="AX71" t="inlineStr"/>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr"/>
+      <c r="BA71" t="inlineStr"/>
+      <c r="BB71" t="inlineStr"/>
+      <c r="BC71" t="inlineStr"/>
+      <c r="BD71" t="inlineStr"/>
+      <c r="BE71" t="inlineStr"/>
+      <c r="BF71" t="inlineStr"/>
+      <c r="BG71" t="inlineStr"/>
+      <c r="BH71" t="inlineStr"/>
+      <c r="BI71" t="inlineStr"/>
+      <c r="BJ71" t="inlineStr"/>
+      <c r="BK71" t="inlineStr"/>
+      <c r="BL71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MZ0902</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>MZ0911</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>66.13</v>
+      </c>
+      <c r="I72" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="J72" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>43.06</v>
+      </c>
+      <c r="M72" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr"/>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr"/>
+      <c r="AJ72" t="inlineStr"/>
+      <c r="AK72" t="inlineStr"/>
+      <c r="AL72" t="inlineStr"/>
+      <c r="AM72" t="inlineStr"/>
+      <c r="AN72" t="inlineStr"/>
+      <c r="AO72" t="inlineStr"/>
+      <c r="AP72" t="inlineStr"/>
+      <c r="AQ72" t="inlineStr"/>
+      <c r="AR72" t="inlineStr"/>
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AU72" t="inlineStr"/>
+      <c r="AV72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr"/>
+      <c r="AX72" t="inlineStr"/>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr"/>
+      <c r="BA72" t="inlineStr"/>
+      <c r="BB72" t="inlineStr"/>
+      <c r="BC72" t="inlineStr"/>
+      <c r="BD72" t="inlineStr"/>
+      <c r="BE72" t="inlineStr"/>
+      <c r="BF72" t="inlineStr"/>
+      <c r="BG72" t="inlineStr"/>
+      <c r="BH72" t="inlineStr"/>
+      <c r="BI72" t="inlineStr"/>
+      <c r="BJ72" t="inlineStr"/>
+      <c r="BK72" t="inlineStr"/>
+      <c r="BL72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>MZ0905</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>MZ0811</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>83.97</v>
+      </c>
+      <c r="I73" t="n">
+        <v>15.61</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="inlineStr"/>
+      <c r="AD73" t="inlineStr"/>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="inlineStr"/>
+      <c r="AK73" t="inlineStr"/>
+      <c r="AL73" t="inlineStr"/>
+      <c r="AM73" t="inlineStr"/>
+      <c r="AN73" t="inlineStr"/>
+      <c r="AO73" t="inlineStr"/>
+      <c r="AP73" t="inlineStr"/>
+      <c r="AQ73" t="inlineStr"/>
+      <c r="AR73" t="inlineStr"/>
+      <c r="AS73" t="inlineStr"/>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AU73" t="inlineStr"/>
+      <c r="AV73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr"/>
+      <c r="AX73" t="inlineStr"/>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr"/>
+      <c r="BA73" t="inlineStr"/>
+      <c r="BB73" t="inlineStr"/>
+      <c r="BC73" t="inlineStr"/>
+      <c r="BD73" t="inlineStr"/>
+      <c r="BE73" t="inlineStr"/>
+      <c r="BF73" t="inlineStr"/>
+      <c r="BG73" t="inlineStr"/>
+      <c r="BH73" t="inlineStr"/>
+      <c r="BI73" t="inlineStr"/>
+      <c r="BJ73" t="inlineStr"/>
+      <c r="BK73" t="inlineStr"/>
+      <c r="BL73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MZ0906</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="inlineStr"/>
+      <c r="AD74" t="inlineStr"/>
+      <c r="AE74" t="inlineStr"/>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="inlineStr"/>
+      <c r="AH74" t="inlineStr"/>
+      <c r="AI74" t="inlineStr"/>
+      <c r="AJ74" t="inlineStr"/>
+      <c r="AK74" t="inlineStr"/>
+      <c r="AL74" t="inlineStr"/>
+      <c r="AM74" t="inlineStr"/>
+      <c r="AN74" t="inlineStr"/>
+      <c r="AO74" t="inlineStr"/>
+      <c r="AP74" t="inlineStr"/>
+      <c r="AQ74" t="inlineStr"/>
+      <c r="AR74" t="inlineStr"/>
+      <c r="AS74" t="inlineStr"/>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AU74" t="inlineStr"/>
+      <c r="AV74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr"/>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Sofala</t>
+        </is>
+      </c>
+      <c r="AY74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ74" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>MZ09</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr"/>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>Protests ---- Riots ---- Riots ---- Protests</t>
+        </is>
+      </c>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Violent demonstration ---- Violent demonstration ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE74" t="inlineStr">
+        <is>
+          <t>Protesters (Mozambique) ---- Rioters (Mozambique) ---- Rioters (Mozambique) ---- Protesters (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BF74" t="inlineStr">
+        <is>
+          <t>Students (Mozambique) ---- PODEMOS: Optimistic Party for the Development of Mozambique ---- PODEMOS: Optimistic Party for the Development of Mozambique ---- Teachers (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BG74" t="inlineStr">
+        <is>
+          <t>Police Forces of Mozambique (1990-) ---- Police Forces of Mozambique (1990-)</t>
+        </is>
+      </c>
+      <c r="BH74" t="inlineStr"/>
+      <c r="BI74" t="inlineStr">
+        <is>
+          <t>Around 10 July 2024 (as reported), IFAPA (Training Institute for Public and Municipal Administration) students protested in Beira (Cidade da Beira, Sofala) against a delay upon completion of courses. ---- On 21 October 2024, dozens of PODEMOS supporters barricaded a road with burning tires during a demonstration in Beira (Cidade da Beira, Sofala), following a call by the PODEMOS presidential candidate for a national strike. The demonstration was held over claims of the assassination of the PODEMOS presidential candidate's legal adviser and legal representative by special forces (coded separately), and what they consider fraudulent general election results. Police officers intervened firing shots, clearing barricades, and detaining at least 3 people (conflicting reports ranging between 3 and 17). Injuries unknown/not reported. Shops, markets, and schools were closed. Police patrolled the city. There were demonstrations in Moatize, Nacala, Quelimane, Tete, Pemba, and Maputo (coded separately). The incident happened during the vote counting of the 2024 general election. ---- On 24 October 2024, PODEMOS supporters burned tires on a public road and burned six improvised classrooms during a demonstration in Beira (Cidade da Beira, Sofala), following a call by the PODEMOS presidential candidate for a two-day national strike. The demonstration was held against police violence during previous PODEMOS-led demonstrations, claims of the assassination of the PODEMOS presidential candidate's legal adviser and legal representative by special forces (coded separately), and what they consider fraudulent general election results. Police officers intervened (means unspecified). Schools and some shops closed. According to the spokesperson for the General Command of the police, during the 24 October demonstrations, across the country, at least 20 people were injured, and 371 were detained by police forces. ---- On 18 December 2024, around 100 striking literacy teachers demonstrated outside the education sector building in Beira (Cidade Da Beira, Sofala), demanding payment for their 3 years in arrears of subsidies.</t>
+        </is>
+      </c>
+      <c r="BJ74" t="inlineStr">
+        <is>
+          <t>2024-07-10 ---- 2024-10-21 ---- 2024-10-24 ---- 2024-12-18</t>
+        </is>
+      </c>
+      <c r="BK74" t="inlineStr">
+        <is>
+          <t>Cidade Da Beira</t>
+        </is>
+      </c>
+      <c r="BL74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MZ0907</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>MZ0715</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>MZ0715;MZ0907;MZ0913</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>84.84999999999999</v>
+      </c>
+      <c r="I75" t="n">
+        <v>15.15</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr"/>
+      <c r="AC75" t="inlineStr"/>
+      <c r="AD75" t="inlineStr"/>
+      <c r="AE75" t="inlineStr"/>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="inlineStr"/>
+      <c r="AH75" t="inlineStr"/>
+      <c r="AI75" t="inlineStr"/>
+      <c r="AJ75" t="inlineStr"/>
+      <c r="AK75" t="inlineStr"/>
+      <c r="AL75" t="inlineStr"/>
+      <c r="AM75" t="inlineStr"/>
+      <c r="AN75" t="inlineStr"/>
+      <c r="AO75" t="inlineStr"/>
+      <c r="AP75" t="inlineStr"/>
+      <c r="AQ75" t="inlineStr"/>
+      <c r="AR75" t="inlineStr"/>
+      <c r="AS75" t="inlineStr"/>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AU75" t="inlineStr"/>
+      <c r="AV75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr"/>
+      <c r="AX75" t="inlineStr"/>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr"/>
+      <c r="BA75" t="inlineStr"/>
+      <c r="BB75" t="inlineStr"/>
+      <c r="BC75" t="inlineStr"/>
+      <c r="BD75" t="inlineStr"/>
+      <c r="BE75" t="inlineStr"/>
+      <c r="BF75" t="inlineStr"/>
+      <c r="BG75" t="inlineStr"/>
+      <c r="BH75" t="inlineStr"/>
+      <c r="BI75" t="inlineStr"/>
+      <c r="BJ75" t="inlineStr"/>
+      <c r="BK75" t="inlineStr"/>
+      <c r="BL75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>MZ0911</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>MZ0902</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>76.19</v>
+      </c>
+      <c r="I76" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr"/>
+      <c r="AC76" t="inlineStr"/>
+      <c r="AD76" t="inlineStr"/>
+      <c r="AE76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="inlineStr"/>
+      <c r="AH76" t="inlineStr"/>
+      <c r="AI76" t="inlineStr"/>
+      <c r="AJ76" t="inlineStr"/>
+      <c r="AK76" t="inlineStr"/>
+      <c r="AL76" t="inlineStr"/>
+      <c r="AM76" t="inlineStr"/>
+      <c r="AN76" t="inlineStr"/>
+      <c r="AO76" t="inlineStr"/>
+      <c r="AP76" t="inlineStr"/>
+      <c r="AQ76" t="inlineStr"/>
+      <c r="AR76" t="inlineStr"/>
+      <c r="AS76" t="inlineStr"/>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AU76" t="inlineStr"/>
+      <c r="AV76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr"/>
+      <c r="AX76" t="inlineStr"/>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr"/>
+      <c r="BA76" t="inlineStr"/>
+      <c r="BB76" t="inlineStr"/>
+      <c r="BC76" t="inlineStr"/>
+      <c r="BD76" t="inlineStr"/>
+      <c r="BE76" t="inlineStr"/>
+      <c r="BF76" t="inlineStr"/>
+      <c r="BG76" t="inlineStr"/>
+      <c r="BH76" t="inlineStr"/>
+      <c r="BI76" t="inlineStr"/>
+      <c r="BJ76" t="inlineStr"/>
+      <c r="BK76" t="inlineStr"/>
+      <c r="BL76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>MZ0913</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>MZ0715</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>MZ0715;MZ0907;MZ0913</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>86.17</v>
+      </c>
+      <c r="I77" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="J77" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="inlineStr"/>
+      <c r="AD77" t="inlineStr"/>
+      <c r="AE77" t="inlineStr"/>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="inlineStr"/>
+      <c r="AH77" t="inlineStr"/>
+      <c r="AI77" t="inlineStr"/>
+      <c r="AJ77" t="inlineStr"/>
+      <c r="AK77" t="inlineStr"/>
+      <c r="AL77" t="inlineStr"/>
+      <c r="AM77" t="inlineStr"/>
+      <c r="AN77" t="inlineStr"/>
+      <c r="AO77" t="inlineStr"/>
+      <c r="AP77" t="inlineStr"/>
+      <c r="AQ77" t="inlineStr"/>
+      <c r="AR77" t="inlineStr"/>
+      <c r="AS77" t="inlineStr"/>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AU77" t="inlineStr"/>
+      <c r="AV77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr"/>
+      <c r="AX77" t="inlineStr"/>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr"/>
+      <c r="BA77" t="inlineStr"/>
+      <c r="BB77" t="inlineStr"/>
+      <c r="BC77" t="inlineStr"/>
+      <c r="BD77" t="inlineStr"/>
+      <c r="BE77" t="inlineStr"/>
+      <c r="BF77" t="inlineStr"/>
+      <c r="BG77" t="inlineStr"/>
+      <c r="BH77" t="inlineStr"/>
+      <c r="BI77" t="inlineStr"/>
+      <c r="BJ77" t="inlineStr"/>
+      <c r="BK77" t="inlineStr"/>
+      <c r="BL77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>MZ1006</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>MZ0810</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>84.92</v>
+      </c>
+      <c r="I78" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="J78" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="K78" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="L78" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="inlineStr"/>
+      <c r="AD78" t="inlineStr"/>
+      <c r="AE78" t="inlineStr"/>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="inlineStr"/>
+      <c r="AH78" t="inlineStr"/>
+      <c r="AI78" t="inlineStr"/>
+      <c r="AJ78" t="inlineStr"/>
+      <c r="AK78" t="inlineStr"/>
+      <c r="AL78" t="inlineStr"/>
+      <c r="AM78" t="inlineStr"/>
+      <c r="AN78" t="inlineStr"/>
+      <c r="AO78" t="inlineStr"/>
+      <c r="AP78" t="inlineStr"/>
+      <c r="AQ78" t="inlineStr"/>
+      <c r="AR78" t="inlineStr"/>
+      <c r="AS78" t="inlineStr"/>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AU78" t="inlineStr"/>
+      <c r="AV78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr"/>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Tete</t>
+        </is>
+      </c>
+      <c r="AY78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>MZ10</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr"/>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>Protests ---- Protests ---- Riots</t>
+        </is>
+      </c>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Excessive force against protesters ---- Violent demonstration</t>
+        </is>
+      </c>
+      <c r="BE78" t="inlineStr">
+        <is>
+          <t>Protesters (Mozambique) ---- Protesters (Mozambique) ---- Rioters (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BF78" t="inlineStr">
+        <is>
+          <t>Students (Mozambique) ---- PODEMOS: Optimistic Party for the Development of Mozambique ---- PODEMOS: Optimistic Party for the Development of Mozambique</t>
+        </is>
+      </c>
+      <c r="BG78" t="inlineStr">
+        <is>
+          <t>Police Forces of Mozambique (1990-)</t>
+        </is>
+      </c>
+      <c r="BH78" t="inlineStr"/>
+      <c r="BI78" t="inlineStr">
+        <is>
+          <t>On 14 September 2024, more than 100 medical students who attended the Faculty of Health Sciences at the University of Zambeze marched in Tete (Tete, Tete) against alleged lack of contracts for integrated internships. Students marched from the installations of Unizambeze to Independence Square. Students complained about lack of communication and alleged imposition of contracts to access the integrated internships, accusing the institution's management of acting outside the law. ---- On 4 November 2024, PODEMOS supporters demonstrated in Tete (Tete, Tete), following a call by the PODEMOS presidential candidate for a seven-day national strike and protests. The demonstration was held to protest police violence during previous PODEMOS-led demonstrations, claims of the assassination of the PODEMOS presidential candidate's legal adviser and legal representative by special forces (coded separately), and what they consider fraudulent general election results. Police officers intervened firing tear gas at the ground of Castro Teofilo school. Center for Public Integrity (CJP) claimed one person was killed. The incident happened after the announcement of the final results of the 2024 general election. ---- Around 25 January 2025 (as reported), PODEMOS supporters destroyed at least 5 schools, including the Cateme secondary school, the Benga basic school, and the Oitavadas basic school during a demonstration in Tete province (Tete, Tete). In the Cateme secondary school, the library, the computer room, and the administrative block were vandalized. The event happened in the context of nationwide demonstrations and unrest against election results.</t>
+        </is>
+      </c>
+      <c r="BJ78" t="inlineStr">
+        <is>
+          <t>2024-09-14 ---- 2024-11-04 ---- 2025-01-25</t>
+        </is>
+      </c>
+      <c r="BK78" t="inlineStr">
+        <is>
+          <t>Tete</t>
+        </is>
+      </c>
+      <c r="BL78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MZ1012</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="inlineStr"/>
+      <c r="AD79" t="inlineStr"/>
+      <c r="AE79" t="inlineStr"/>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="inlineStr"/>
+      <c r="AH79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr"/>
+      <c r="AJ79" t="inlineStr"/>
+      <c r="AK79" t="inlineStr"/>
+      <c r="AL79" t="inlineStr"/>
+      <c r="AM79" t="inlineStr"/>
+      <c r="AN79" t="inlineStr"/>
+      <c r="AO79" t="inlineStr"/>
+      <c r="AP79" t="inlineStr"/>
+      <c r="AQ79" t="inlineStr"/>
+      <c r="AR79" t="inlineStr"/>
+      <c r="AS79" t="inlineStr"/>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AU79" t="inlineStr"/>
+      <c r="AV79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr"/>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Tete</t>
+        </is>
+      </c>
+      <c r="AY79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>MZ10</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr"/>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>Riots</t>
+        </is>
+      </c>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>Violent demonstration</t>
+        </is>
+      </c>
+      <c r="BE79" t="inlineStr">
+        <is>
+          <t>Rioters (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BF79" t="inlineStr">
+        <is>
+          <t>PODEMOS: Optimistic Party for the Development of Mozambique</t>
+        </is>
+      </c>
+      <c r="BG79" t="inlineStr"/>
+      <c r="BH79" t="inlineStr"/>
+      <c r="BI79" t="inlineStr">
+        <is>
+          <t>Around 25 January 2025 (as reported), PODEMOS supporters destroyed at least 3 schools, including the Necungas primary school and the Mutarara Moatize basic school during a demonstration in the Moatize district (Moatize, Tete). The event happened in the context of nationwide demonstrations and unrest against election results.</t>
+        </is>
+      </c>
+      <c r="BJ79" t="inlineStr">
+        <is>
+          <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="BK79" t="inlineStr">
+        <is>
+          <t>Moatize</t>
+        </is>
+      </c>
+      <c r="BL79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MZ1013</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>MZ1113</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>78.34</v>
+      </c>
+      <c r="I80" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="L80" t="n">
+        <v>44.17</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr"/>
+      <c r="AJ80" t="inlineStr"/>
+      <c r="AK80" t="inlineStr"/>
+      <c r="AL80" t="inlineStr"/>
+      <c r="AM80" t="inlineStr"/>
+      <c r="AN80" t="inlineStr"/>
+      <c r="AO80" t="inlineStr"/>
+      <c r="AP80" t="inlineStr"/>
+      <c r="AQ80" t="inlineStr"/>
+      <c r="AR80" t="inlineStr"/>
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AU80" t="inlineStr"/>
+      <c r="AV80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr"/>
+      <c r="AX80" t="inlineStr"/>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr"/>
+      <c r="BA80" t="inlineStr"/>
+      <c r="BB80" t="inlineStr"/>
+      <c r="BC80" t="inlineStr"/>
+      <c r="BD80" t="inlineStr"/>
+      <c r="BE80" t="inlineStr"/>
+      <c r="BF80" t="inlineStr"/>
+      <c r="BG80" t="inlineStr"/>
+      <c r="BH80" t="inlineStr"/>
+      <c r="BI80" t="inlineStr"/>
+      <c r="BJ80" t="inlineStr"/>
+      <c r="BK80" t="inlineStr"/>
+      <c r="BL80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MZ1101</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>MZ0708</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>93.33</v>
+      </c>
+      <c r="I81" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr"/>
+      <c r="AH81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr"/>
+      <c r="AJ81" t="inlineStr"/>
+      <c r="AK81" t="inlineStr"/>
+      <c r="AL81" t="inlineStr"/>
+      <c r="AM81" t="inlineStr"/>
+      <c r="AN81" t="inlineStr"/>
+      <c r="AO81" t="inlineStr"/>
+      <c r="AP81" t="inlineStr"/>
+      <c r="AQ81" t="inlineStr"/>
+      <c r="AR81" t="inlineStr"/>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AU81" t="inlineStr"/>
+      <c r="AV81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr"/>
+      <c r="AX81" t="inlineStr"/>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr"/>
+      <c r="BA81" t="inlineStr"/>
+      <c r="BB81" t="inlineStr"/>
+      <c r="BC81" t="inlineStr"/>
+      <c r="BD81" t="inlineStr"/>
+      <c r="BE81" t="inlineStr"/>
+      <c r="BF81" t="inlineStr"/>
+      <c r="BG81" t="inlineStr"/>
+      <c r="BH81" t="inlineStr"/>
+      <c r="BI81" t="inlineStr"/>
+      <c r="BJ81" t="inlineStr"/>
+      <c r="BK81" t="inlineStr"/>
+      <c r="BL81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MZ1106</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>MZ0713</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>80</v>
+      </c>
+      <c r="I82" t="n">
+        <v>20</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>31.27</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr"/>
+      <c r="AC82" t="inlineStr"/>
+      <c r="AD82" t="inlineStr"/>
+      <c r="AE82" t="inlineStr"/>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="inlineStr"/>
+      <c r="AH82" t="inlineStr"/>
+      <c r="AI82" t="inlineStr"/>
+      <c r="AJ82" t="inlineStr"/>
+      <c r="AK82" t="inlineStr"/>
+      <c r="AL82" t="inlineStr"/>
+      <c r="AM82" t="inlineStr"/>
+      <c r="AN82" t="inlineStr"/>
+      <c r="AO82" t="inlineStr"/>
+      <c r="AP82" t="inlineStr"/>
+      <c r="AQ82" t="inlineStr"/>
+      <c r="AR82" t="inlineStr"/>
+      <c r="AS82" t="inlineStr"/>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AU82" t="inlineStr"/>
+      <c r="AV82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr"/>
+      <c r="AX82" t="inlineStr"/>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr"/>
+      <c r="BA82" t="inlineStr"/>
+      <c r="BB82" t="inlineStr"/>
+      <c r="BC82" t="inlineStr"/>
+      <c r="BD82" t="inlineStr"/>
+      <c r="BE82" t="inlineStr"/>
+      <c r="BF82" t="inlineStr"/>
+      <c r="BG82" t="inlineStr"/>
+      <c r="BH82" t="inlineStr"/>
+      <c r="BI82" t="inlineStr"/>
+      <c r="BJ82" t="inlineStr"/>
+      <c r="BK82" t="inlineStr"/>
+      <c r="BL82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>MZ1111</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>MZ0813</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>86.17</v>
+      </c>
+      <c r="I83" t="n">
+        <v>12.77</v>
+      </c>
+      <c r="J83" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>30.22</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" t="inlineStr"/>
+      <c r="X83" t="inlineStr"/>
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr"/>
+      <c r="AA83" t="inlineStr"/>
+      <c r="AB83" t="inlineStr"/>
+      <c r="AC83" t="inlineStr"/>
+      <c r="AD83" t="inlineStr"/>
+      <c r="AE83" t="inlineStr"/>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="inlineStr"/>
+      <c r="AH83" t="inlineStr"/>
+      <c r="AI83" t="inlineStr"/>
+      <c r="AJ83" t="inlineStr"/>
+      <c r="AK83" t="inlineStr"/>
+      <c r="AL83" t="inlineStr"/>
+      <c r="AM83" t="inlineStr"/>
+      <c r="AN83" t="inlineStr"/>
+      <c r="AO83" t="inlineStr"/>
+      <c r="AP83" t="inlineStr"/>
+      <c r="AQ83" t="inlineStr"/>
+      <c r="AR83" t="inlineStr"/>
+      <c r="AS83" t="inlineStr"/>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AU83" t="inlineStr"/>
+      <c r="AV83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr"/>
+      <c r="AX83" t="inlineStr"/>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr"/>
+      <c r="BA83" t="inlineStr"/>
+      <c r="BB83" t="inlineStr"/>
+      <c r="BC83" t="inlineStr"/>
+      <c r="BD83" t="inlineStr"/>
+      <c r="BE83" t="inlineStr"/>
+      <c r="BF83" t="inlineStr"/>
+      <c r="BG83" t="inlineStr"/>
+      <c r="BH83" t="inlineStr"/>
+      <c r="BI83" t="inlineStr"/>
+      <c r="BJ83" t="inlineStr"/>
+      <c r="BK83" t="inlineStr"/>
+      <c r="BL83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MZ1113</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>MZ1013</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>96.88</v>
+      </c>
+      <c r="I84" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr"/>
+      <c r="Y84" t="inlineStr"/>
+      <c r="Z84" t="inlineStr"/>
+      <c r="AA84" t="inlineStr"/>
+      <c r="AB84" t="inlineStr"/>
+      <c r="AC84" t="inlineStr"/>
+      <c r="AD84" t="inlineStr"/>
+      <c r="AE84" t="inlineStr"/>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="inlineStr"/>
+      <c r="AH84" t="inlineStr"/>
+      <c r="AI84" t="inlineStr"/>
+      <c r="AJ84" t="inlineStr"/>
+      <c r="AK84" t="inlineStr"/>
+      <c r="AL84" t="inlineStr"/>
+      <c r="AM84" t="inlineStr"/>
+      <c r="AN84" t="inlineStr"/>
+      <c r="AO84" t="inlineStr"/>
+      <c r="AP84" t="inlineStr"/>
+      <c r="AQ84" t="inlineStr"/>
+      <c r="AR84" t="inlineStr"/>
+      <c r="AS84" t="inlineStr"/>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AU84" t="inlineStr"/>
+      <c r="AV84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr"/>
+      <c r="AX84" t="inlineStr"/>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr"/>
+      <c r="BA84" t="inlineStr"/>
+      <c r="BB84" t="inlineStr"/>
+      <c r="BC84" t="inlineStr"/>
+      <c r="BD84" t="inlineStr"/>
+      <c r="BE84" t="inlineStr"/>
+      <c r="BF84" t="inlineStr"/>
+      <c r="BG84" t="inlineStr"/>
+      <c r="BH84" t="inlineStr"/>
+      <c r="BI84" t="inlineStr"/>
+      <c r="BJ84" t="inlineStr"/>
+      <c r="BK84" t="inlineStr"/>
+      <c r="BL84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MZ1114</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>MZ0802</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>MZ0102;MZ0103;MZ0104;MZ0111;MZ0114;MZ0401;MZ0701;MZ0703;MZ0704;MZ0707;MZ0710;MZ0712;MZ0716;MZ0722;MZ0801;MZ0802;MZ0803;MZ0806;MZ0808;MZ0809;MZ0812;MZ0813;MZ0817;MZ0819;MZ1111;MZ1114</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>90.31999999999999</v>
+      </c>
+      <c r="I85" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="J85" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="V85" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" t="inlineStr"/>
+      <c r="X85" t="inlineStr"/>
+      <c r="Y85" t="inlineStr"/>
+      <c r="Z85" t="inlineStr"/>
+      <c r="AA85" t="inlineStr"/>
+      <c r="AB85" t="inlineStr"/>
+      <c r="AC85" t="inlineStr"/>
+      <c r="AD85" t="inlineStr"/>
+      <c r="AE85" t="inlineStr"/>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="inlineStr"/>
+      <c r="AH85" t="inlineStr"/>
+      <c r="AI85" t="inlineStr"/>
+      <c r="AJ85" t="inlineStr"/>
+      <c r="AK85" t="inlineStr"/>
+      <c r="AL85" t="inlineStr"/>
+      <c r="AM85" t="inlineStr"/>
+      <c r="AN85" t="inlineStr"/>
+      <c r="AO85" t="inlineStr"/>
+      <c r="AP85" t="inlineStr"/>
+      <c r="AQ85" t="inlineStr"/>
+      <c r="AR85" t="inlineStr"/>
+      <c r="AS85" t="inlineStr"/>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AU85" t="inlineStr"/>
+      <c r="AV85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr"/>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Zambezia</t>
+        </is>
+      </c>
+      <c r="AY85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA85" t="inlineStr">
+        <is>
+          <t>MZ11</t>
+        </is>
+      </c>
+      <c r="BB85" t="inlineStr"/>
+      <c r="BC85" t="inlineStr">
+        <is>
+          <t>Riots</t>
+        </is>
+      </c>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>Mob violence</t>
+        </is>
+      </c>
+      <c r="BE85" t="inlineStr">
+        <is>
+          <t>Rioters (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BF85" t="inlineStr">
+        <is>
+          <t>Vigilante Group (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BG85" t="inlineStr">
+        <is>
+          <t>Civilians (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BH85" t="inlineStr">
+        <is>
+          <t>Teachers (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BI85" t="inlineStr">
+        <is>
+          <t>Around 19 July 2025 (as reported), residents beat 4 teachers in Cubeliua neighborhood of Mocuba (Mocuba, Zambezia), accusing them of trafficking albinos and their organs. No deaths reported.</t>
+        </is>
+      </c>
+      <c r="BJ85" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="BK85" t="inlineStr">
+        <is>
+          <t>Mocuba</t>
+        </is>
+      </c>
+      <c r="BL85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>MZ1120</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>MZ0818</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>MZ0818;MZ1120</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>89.38</v>
+      </c>
+      <c r="I86" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="L86" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr"/>
+      <c r="Y86" t="inlineStr"/>
+      <c r="Z86" t="inlineStr"/>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr"/>
+      <c r="AC86" t="inlineStr"/>
+      <c r="AD86" t="inlineStr"/>
+      <c r="AE86" t="inlineStr"/>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="inlineStr"/>
+      <c r="AH86" t="inlineStr"/>
+      <c r="AI86" t="inlineStr"/>
+      <c r="AJ86" t="inlineStr"/>
+      <c r="AK86" t="inlineStr"/>
+      <c r="AL86" t="inlineStr"/>
+      <c r="AM86" t="inlineStr"/>
+      <c r="AN86" t="inlineStr"/>
+      <c r="AO86" t="inlineStr"/>
+      <c r="AP86" t="inlineStr"/>
+      <c r="AQ86" t="inlineStr"/>
+      <c r="AR86" t="inlineStr"/>
+      <c r="AS86" t="inlineStr"/>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AU86" t="inlineStr"/>
+      <c r="AV86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr"/>
+      <c r="AX86" t="inlineStr"/>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr"/>
+      <c r="BA86" t="inlineStr"/>
+      <c r="BB86" t="inlineStr"/>
+      <c r="BC86" t="inlineStr"/>
+      <c r="BD86" t="inlineStr"/>
+      <c r="BE86" t="inlineStr"/>
+      <c r="BF86" t="inlineStr"/>
+      <c r="BG86" t="inlineStr"/>
+      <c r="BH86" t="inlineStr"/>
+      <c r="BI86" t="inlineStr"/>
+      <c r="BJ86" t="inlineStr"/>
+      <c r="BK86" t="inlineStr"/>
+      <c r="BL86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>MZ1122</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>MZ0709</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>MZ0101;MZ0105;MZ0108;MZ0109;MZ0112;MZ0113;MZ0115;MZ0116;MZ0207;MZ0301;MZ0305;MZ0402;MZ0410;MZ0702;MZ0708;MZ0709;MZ0713;MZ0717;MZ0718;MZ0719;MZ0720;MZ0721;MZ0723;MZ0810;MZ0811;MZ0814;MZ0815;MZ0901;MZ0902;MZ0905;MZ0911;MZ1006;MZ1013;MZ1101;MZ1106;MZ1113;MZ1122</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="I87" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="J87" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>20.69</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U87" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr"/>
+      <c r="AA87" t="inlineStr"/>
+      <c r="AB87" t="inlineStr"/>
+      <c r="AC87" t="inlineStr"/>
+      <c r="AD87" t="inlineStr"/>
+      <c r="AE87" t="inlineStr"/>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="inlineStr"/>
+      <c r="AH87" t="inlineStr"/>
+      <c r="AI87" t="inlineStr"/>
+      <c r="AJ87" t="inlineStr"/>
+      <c r="AK87" t="inlineStr"/>
+      <c r="AL87" t="inlineStr"/>
+      <c r="AM87" t="inlineStr"/>
+      <c r="AN87" t="inlineStr"/>
+      <c r="AO87" t="inlineStr"/>
+      <c r="AP87" t="inlineStr"/>
+      <c r="AQ87" t="inlineStr"/>
+      <c r="AR87" t="inlineStr"/>
+      <c r="AS87" t="inlineStr"/>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AU87" t="inlineStr"/>
+      <c r="AV87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr"/>
+      <c r="AX87" t="inlineStr"/>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr"/>
+      <c r="BA87" t="inlineStr"/>
+      <c r="BB87" t="inlineStr"/>
+      <c r="BC87" t="inlineStr"/>
+      <c r="BD87" t="inlineStr"/>
+      <c r="BE87" t="inlineStr"/>
+      <c r="BF87" t="inlineStr"/>
+      <c r="BG87" t="inlineStr"/>
+      <c r="BH87" t="inlineStr"/>
+      <c r="BI87" t="inlineStr"/>
+      <c r="BJ87" t="inlineStr"/>
+      <c r="BK87" t="inlineStr"/>
+      <c r="BL87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>MZ1123</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="inlineStr"/>
+      <c r="AA88" t="inlineStr"/>
+      <c r="AB88" t="inlineStr"/>
+      <c r="AC88" t="inlineStr"/>
+      <c r="AD88" t="inlineStr"/>
+      <c r="AE88" t="inlineStr"/>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="inlineStr"/>
+      <c r="AH88" t="inlineStr"/>
+      <c r="AI88" t="inlineStr"/>
+      <c r="AJ88" t="inlineStr"/>
+      <c r="AK88" t="inlineStr"/>
+      <c r="AL88" t="inlineStr"/>
+      <c r="AM88" t="inlineStr"/>
+      <c r="AN88" t="inlineStr"/>
+      <c r="AO88" t="inlineStr"/>
+      <c r="AP88" t="inlineStr"/>
+      <c r="AQ88" t="inlineStr"/>
+      <c r="AR88" t="inlineStr"/>
+      <c r="AS88" t="inlineStr"/>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AU88" t="inlineStr"/>
+      <c r="AV88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr"/>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Zambezia</t>
+        </is>
+      </c>
+      <c r="AY88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ88" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA88" t="inlineStr">
+        <is>
+          <t>MZ11</t>
+        </is>
+      </c>
+      <c r="BB88" t="inlineStr"/>
+      <c r="BC88" t="inlineStr">
+        <is>
+          <t>Riots ---- Riots</t>
+        </is>
+      </c>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>Violent demonstration ---- Violent demonstration</t>
+        </is>
+      </c>
+      <c r="BE88" t="inlineStr">
+        <is>
+          <t>Rioters (Mozambique) ---- Rioters (Mozambique)</t>
+        </is>
+      </c>
+      <c r="BF88" t="inlineStr">
+        <is>
+          <t>PODEMOS: Optimistic Party for the Development of Mozambique ---- PODEMOS: Optimistic Party for the Development of Mozambique</t>
+        </is>
+      </c>
+      <c r="BG88" t="inlineStr">
+        <is>
+          <t>Police Forces of Mozambique (1990-)</t>
+        </is>
+      </c>
+      <c r="BH88" t="inlineStr"/>
+      <c r="BI88" t="inlineStr">
+        <is>
+          <t>On 31 October 2024, PODEMOS supporters destroyed three classrooms of a primary school and the FRELIMO District Committee in Pebane (Pebane, Zambezia), following a call by the PODEMOS presidential candidate for a seven-day national strike. The demonstration was held against police violence during previous PODEMOS-led demonstrations, claims of the assassination of the PODEMOS presidential candidate's legal adviser and legal representative by special forces (coded separately), and what they consider fraudulent general election results. Police forces intervened firing live bullets. Three people were injured and admitted to a hospital. The head of the Public Relations Department of the Provincial Command of the Police said that rioters were being accompanied by the police, but halfway along the route, they split into three groups. One group vandalized the primary school, the other the FRELIMO District Committee, and the third group intended to break into the police station. The incident happened after the announcement of the final results of the 2024 general election. ---- On 23 December 2024, hundreds of PODEMOS supporters blocked (means unspecified) the main roads in the district of Pebane (Pebane, Zambezia), following a call by the PODEMOS presidential candidate after the announcement by the Constitutional Council of the victory of the FRELIMO party in the presidential, legislative and provincial elections. Rioters destroyed a secondary school and the district court.</t>
+        </is>
+      </c>
+      <c r="BJ88" t="inlineStr">
+        <is>
+          <t>2024-10-31 ---- 2024-12-23</t>
+        </is>
+      </c>
+      <c r="BK88" t="inlineStr">
+        <is>
+          <t>Pebane</t>
+        </is>
+      </c>
+      <c r="BL88" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9489,13 +11603,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A072D55-7272-45EE-8059-90FC5E16F948}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72B3F250-C23C-4EC2-BA00-26658C8CB401}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05A962EC-D45F-4CE7-B452-6B578A0EFF4B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5875B30-F696-425C-82CA-BB4F2BDE8B28}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{472F697A-B245-462C-91F0-BA79E9660FB0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8148837-E4AA-44F7-88B9-3F3DCD8013EF}"/>
 </file>